--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -9,22 +9,23 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="1"/>
+    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
-    <sheet name="2026-02" sheetId="14" r:id="rId2"/>
-    <sheet name="2026-01" sheetId="13" r:id="rId3"/>
-    <sheet name="2025-12" sheetId="12" r:id="rId4"/>
-    <sheet name="2025-11" sheetId="11" r:id="rId5"/>
-    <sheet name="2025-10" sheetId="10" r:id="rId6"/>
-    <sheet name="2025-09" sheetId="9" r:id="rId7"/>
-    <sheet name="2025-08" sheetId="8" r:id="rId8"/>
-    <sheet name="2025-07" sheetId="7" r:id="rId9"/>
-    <sheet name="2025-06" sheetId="6" r:id="rId10"/>
-    <sheet name="2025-05" sheetId="5" r:id="rId11"/>
-    <sheet name="2025-04" sheetId="4" r:id="rId12"/>
-    <sheet name="2025-03" sheetId="1" r:id="rId13"/>
+    <sheet name="2026-03" sheetId="15" r:id="rId2"/>
+    <sheet name="2026-02" sheetId="14" r:id="rId3"/>
+    <sheet name="2026-01" sheetId="13" r:id="rId4"/>
+    <sheet name="2025-12" sheetId="12" r:id="rId5"/>
+    <sheet name="2025-11" sheetId="11" r:id="rId6"/>
+    <sheet name="2025-10" sheetId="10" r:id="rId7"/>
+    <sheet name="2025-09" sheetId="9" r:id="rId8"/>
+    <sheet name="2025-08" sheetId="8" r:id="rId9"/>
+    <sheet name="2025-07" sheetId="7" r:id="rId10"/>
+    <sheet name="2025-06" sheetId="6" r:id="rId11"/>
+    <sheet name="2025-05" sheetId="5" r:id="rId12"/>
+    <sheet name="2025-04" sheetId="4" r:id="rId13"/>
+    <sheet name="2025-03" sheetId="1" r:id="rId14"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -252,7 +253,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -313,11 +314,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="41">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1057,19 +1091,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -1624,17 +1658,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1643,6 +1677,760 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46084</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1659,19 +2447,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -2350,17 +3138,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2369,7 +3157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2386,19 +3174,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3095,17 +3883,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3115,7 +3903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3132,19 +3920,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3773,17 +4561,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3791,7 +4579,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3803,16 +4591,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="19"/>
+      <c r="C2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="20"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="F2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -4461,12 +5249,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4475,6 +5263,616 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46084</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46083</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>46084</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46085</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46086</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46087</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46088</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46089</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46090</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46091</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46092</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46093</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46094</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46095</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46096</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46097</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46098</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46099</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46100</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46101</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46102</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46103</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46104</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46105</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46106</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46107</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46108</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46109</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46110</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46111</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46112</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.5</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>3.3870967741935487E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4491,19 +5889,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5034,16 +6432,20 @@
         <f t="shared" si="1"/>
         <v>46079</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>13</v>
+      </c>
       <c r="H29" s="1">
         <v>20</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
@@ -5051,16 +6453,20 @@
         <f t="shared" si="1"/>
         <v>46080</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>8</v>
+      </c>
       <c r="H30" s="1">
         <v>20</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
@@ -5068,16 +6474,20 @@
         <f t="shared" si="1"/>
         <v>46081</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
       <c r="H31" s="1">
         <v>20</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="4:9" x14ac:dyDescent="0.3">
@@ -5092,12 +6502,12 @@
       <c r="F33" s="5"/>
       <c r="G33" s="1">
         <f>AVERAGE(G4:G31)</f>
-        <v>11.04</v>
+        <v>10.964285714285714</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="5">
         <f>AVERAGE(I4:I31)</f>
-        <v>0.49285714285714288</v>
+        <v>0.54821428571428577</v>
       </c>
     </row>
   </sheetData>
@@ -5107,17 +6517,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5126,7 +6536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5143,19 +6553,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5823,6 +7233,733 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46084</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -5851,734 +7988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46079</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6595,19 +8005,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7265,17 +8675,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7284,7 +8694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7301,19 +8711,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7998,17 +9408,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8017,7 +9427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8034,19 +9444,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8713,17 +10123,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8732,7 +10142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8749,19 +10159,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9449,771 +10859,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46079</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="2"/>
+    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
@@ -354,21 +354,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2411,17 +2411,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3138,17 +3138,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3883,17 +3883,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -4561,17 +4561,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5249,12 +5249,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5339,16 +5339,20 @@
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46084</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>12</v>
+      </c>
       <c r="H6" s="1">
         <v>20</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -5839,12 +5843,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>3.3870967741935487E-2</v>
+        <v>5.32258064516129E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5854,21 +5858,22 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5889,7 +5894,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6517,17 +6522,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6553,7 +6558,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7233,733 +7238,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46084</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -7988,6 +7266,733 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46085</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
@@ -8005,7 +8010,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8675,17 +8680,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8711,7 +8716,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9408,17 +9413,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9444,7 +9449,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10123,17 +10128,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10159,7 +10164,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10859,17 +10864,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5360,16 +5360,20 @@
         <f t="shared" si="1"/>
         <v>46085</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>16</v>
+      </c>
       <c r="H7" s="1">
         <v>20</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -5377,16 +5381,20 @@
         <f t="shared" si="1"/>
         <v>46086</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>8</v>
+      </c>
       <c r="H8" s="1">
         <v>20</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -5843,12 +5851,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>5.32258064516129E-2</v>
+        <v>9.1935483870967741E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5894,7 +5902,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6558,7 +6566,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7283,7 +7291,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8010,7 +8018,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8716,7 +8724,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9449,7 +9457,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10164,7 +10172,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5402,16 +5402,20 @@
         <f t="shared" si="1"/>
         <v>46087</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -5851,12 +5855,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.4</v>
+        <v>11.166666666666666</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>9.1935483870967741E-2</v>
+        <v>0.10806451612903226</v>
       </c>
     </row>
   </sheetData>
@@ -5902,7 +5906,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6566,7 +6570,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7291,7 +7295,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8018,7 +8022,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8724,7 +8728,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9457,7 +9461,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10172,7 +10176,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5423,16 +5423,20 @@
         <f t="shared" si="1"/>
         <v>46088</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
@@ -5440,7 +5444,9 @@
         <f t="shared" si="1"/>
         <v>46089</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>2</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="1"/>
@@ -5846,21 +5852,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0</v>
+        <v>9.6774193548387094E-2</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.10806451612903226</v>
+        <v>0.12419354838709677</v>
       </c>
     </row>
   </sheetData>
@@ -5906,7 +5912,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6570,7 +6576,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7295,7 +7301,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8022,7 +8028,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8728,7 +8734,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9461,7 +9467,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10176,7 +10182,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5449,13 +5449,15 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -5861,12 +5863,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11</v>
+        <v>10.875</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.12419354838709677</v>
+        <v>0.14032258064516129</v>
       </c>
     </row>
   </sheetData>
@@ -5912,7 +5914,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6576,7 +6578,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7301,7 +7303,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8028,7 +8030,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8734,7 +8736,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9467,7 +9469,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10182,7 +10184,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5465,16 +5465,20 @@
         <f t="shared" si="1"/>
         <v>46090</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
@@ -5863,12 +5867,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.875</v>
+        <v>10.777777777777779</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.14032258064516129</v>
+        <v>0.15645161290322579</v>
       </c>
     </row>
   </sheetData>
@@ -5914,7 +5918,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6578,7 +6582,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7303,7 +7307,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8030,7 +8034,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8736,7 +8740,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9469,7 +9473,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10184,7 +10188,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5486,16 +5486,20 @@
         <f t="shared" si="1"/>
         <v>46091</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
@@ -5503,16 +5507,20 @@
         <f t="shared" si="1"/>
         <v>46092</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>10</v>
+      </c>
       <c r="H14" s="1">
         <v>20</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
@@ -5520,16 +5528,20 @@
         <f t="shared" si="1"/>
         <v>46093</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>12</v>
+      </c>
       <c r="H15" s="1">
         <v>20</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
@@ -5867,12 +5879,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.777777777777779</v>
+        <v>10.916666666666666</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.15645161290322579</v>
+        <v>0.21129032258064512</v>
       </c>
     </row>
   </sheetData>
@@ -5918,7 +5930,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6582,7 +6594,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7307,7 +7319,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8034,7 +8046,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8740,7 +8752,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9473,7 +9485,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10188,7 +10200,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5549,16 +5549,20 @@
         <f t="shared" si="1"/>
         <v>46094</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>12</v>
+      </c>
       <c r="H16" s="1">
         <v>20</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
@@ -5566,16 +5570,20 @@
         <f t="shared" si="1"/>
         <v>46095</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
       <c r="H17" s="1">
         <v>20</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
@@ -5583,16 +5591,20 @@
         <f t="shared" si="1"/>
         <v>46096</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>8</v>
+      </c>
       <c r="H18" s="1">
         <v>20</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
@@ -5870,21 +5882,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>9.6774193548387094E-2</v>
+        <v>0.12903225806451613</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.916666666666666</v>
+        <v>10.8</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.21129032258064512</v>
+        <v>0.26129032258064511</v>
       </c>
     </row>
   </sheetData>
@@ -5930,7 +5942,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6594,7 +6606,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7319,7 +7331,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8046,7 +8058,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8752,7 +8764,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9485,7 +9497,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10200,7 +10212,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5612,16 +5612,20 @@
         <f t="shared" si="1"/>
         <v>46097</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>13</v>
+      </c>
       <c r="H19" s="1">
         <v>20</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.3">
@@ -5891,12 +5895,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.8</v>
+        <v>10.9375</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.26129032258064511</v>
+        <v>0.28225806451612895</v>
       </c>
     </row>
   </sheetData>
@@ -5942,7 +5946,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6606,7 +6610,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7331,7 +7335,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8058,7 +8062,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8764,7 +8768,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9497,7 +9501,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10212,7 +10216,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5633,16 +5633,20 @@
         <f t="shared" si="1"/>
         <v>46098</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
       <c r="H20" s="1">
         <v>20</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.3">
@@ -5895,12 +5899,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.9375</v>
+        <v>11.058823529411764</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.28225806451612895</v>
+        <v>0.30322580645161284</v>
       </c>
     </row>
   </sheetData>
@@ -5946,7 +5950,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6610,7 +6614,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7335,7 +7339,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8062,7 +8066,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8768,7 +8772,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9501,7 +9505,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10216,7 +10220,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5654,16 +5654,20 @@
         <f t="shared" si="1"/>
         <v>46099</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>13</v>
+      </c>
       <c r="H21" s="1">
         <v>20</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
@@ -5671,16 +5675,20 @@
         <f t="shared" si="1"/>
         <v>46100</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>13</v>
+      </c>
       <c r="H22" s="1">
         <v>20</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.3">
@@ -5899,12 +5907,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.058823529411764</v>
+        <v>11.263157894736842</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.30322580645161284</v>
+        <v>0.34516129032258064</v>
       </c>
     </row>
   </sheetData>
@@ -5950,7 +5958,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6614,7 +6622,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7339,7 +7347,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8066,7 +8074,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8772,7 +8780,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9505,7 +9513,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10220,7 +10228,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5696,16 +5696,20 @@
         <f t="shared" si="1"/>
         <v>46101</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>14</v>
+      </c>
       <c r="H23" s="1">
         <v>20</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.3">
@@ -5713,16 +5717,20 @@
         <f t="shared" si="1"/>
         <v>46102</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
       <c r="H24" s="1">
         <v>20</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.3">
@@ -5730,16 +5738,20 @@
         <f t="shared" si="1"/>
         <v>46103</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>11</v>
+      </c>
       <c r="H25" s="1">
         <v>20</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.3">
@@ -5898,21 +5910,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.12903225806451613</v>
+        <v>0.16129032258064516</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.263157894736842</v>
+        <v>11.272727272727273</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.34516129032258064</v>
+        <v>0.39999999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -5958,7 +5970,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6622,7 +6634,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7347,7 +7359,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8074,7 +8086,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8780,7 +8792,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9513,7 +9525,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10228,7 +10240,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5759,16 +5759,20 @@
         <f t="shared" si="1"/>
         <v>46104</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>13</v>
+      </c>
       <c r="H26" s="1">
         <v>20</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.3">
@@ -5919,12 +5923,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.272727272727273</v>
+        <v>11.347826086956522</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.39999999999999997</v>
+        <v>0.42096774193548386</v>
       </c>
     </row>
   </sheetData>
@@ -5970,7 +5974,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6634,7 +6638,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7359,7 +7363,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8086,7 +8090,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8792,7 +8796,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9525,7 +9529,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10240,7 +10244,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5780,16 +5780,20 @@
         <f t="shared" si="1"/>
         <v>46105</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>12</v>
+      </c>
       <c r="H27" s="1">
         <v>20</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
@@ -5923,12 +5927,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.347826086956522</v>
+        <v>11.375</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.42096774193548386</v>
+        <v>0.44032258064516122</v>
       </c>
     </row>
   </sheetData>
@@ -5974,7 +5978,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6638,7 +6642,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7363,7 +7367,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8090,7 +8094,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8796,7 +8800,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9529,7 +9533,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10244,7 +10248,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5801,16 +5801,20 @@
         <f t="shared" si="1"/>
         <v>46106</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>12</v>
+      </c>
       <c r="H28" s="1">
         <v>20</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
@@ -5927,12 +5931,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.375</v>
+        <v>11.4</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.44032258064516122</v>
+        <v>0.45967741935483863</v>
       </c>
     </row>
   </sheetData>
@@ -5978,7 +5982,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6642,7 +6646,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7367,7 +7371,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8094,7 +8098,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8800,7 +8804,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9533,7 +9537,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10248,7 +10252,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5822,16 +5822,20 @@
         <f t="shared" si="1"/>
         <v>46107</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>12</v>
+      </c>
       <c r="H29" s="1">
         <v>20</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
@@ -5931,12 +5935,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.4</v>
+        <v>11.423076923076923</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.45967741935483863</v>
+        <v>0.47903225806451605</v>
       </c>
     </row>
   </sheetData>
@@ -5982,7 +5986,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6646,7 +6650,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7371,7 +7375,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8098,7 +8102,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8804,7 +8808,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9537,7 +9541,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10252,7 +10256,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5843,16 +5843,20 @@
         <f t="shared" si="1"/>
         <v>46108</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>14</v>
+      </c>
       <c r="H30" s="1">
         <v>20</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
@@ -5860,16 +5864,20 @@
         <f t="shared" si="1"/>
         <v>46109</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>13</v>
+      </c>
       <c r="H31" s="1">
         <v>20</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
@@ -5877,16 +5885,20 @@
         <f t="shared" si="1"/>
         <v>46110</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1">
+        <v>13</v>
+      </c>
       <c r="H32" s="1">
         <v>20</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
@@ -5935,12 +5947,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.423076923076923</v>
+        <v>11.620689655172415</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.47903225806451605</v>
+        <v>0.543548387096774</v>
       </c>
     </row>
   </sheetData>
@@ -5986,7 +5998,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6650,7 +6662,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7375,7 +7387,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8102,7 +8114,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8808,7 +8820,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9541,7 +9553,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10256,7 +10268,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1091,7 +1091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -1696,7 +1696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -2447,7 +2447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3174,7 +3174,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -3920,7 +3920,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5279,7 +5279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -5906,16 +5906,20 @@
         <f t="shared" si="1"/>
         <v>46111</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1">
+        <v>17</v>
+      </c>
       <c r="H33" s="1">
         <v>20</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.3">
@@ -5938,21 +5942,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.16129032258064516</v>
+        <v>0.19354838709677419</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.620689655172415</v>
+        <v>11.8</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.543548387096774</v>
+        <v>0.57096774193548372</v>
       </c>
     </row>
   </sheetData>
@@ -5998,7 +6002,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -6662,7 +6666,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -7387,7 +7391,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8114,7 +8118,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -8820,7 +8824,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -9553,7 +9557,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">
@@ -10268,7 +10272,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="20" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -325,7 +325,37 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="47">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1125,7 +1155,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1692,17 +1722,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1727,7 +1757,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2418,6 +2448,760 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.44838709677419353</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46114</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="21"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
       </c>
     </row>
   </sheetData>
@@ -2446,760 +3230,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46113</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
@@ -3217,7 +3247,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3908,17 +3938,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3944,7 +3974,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4653,17 +4683,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4690,7 +4720,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -5331,17 +5361,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6019,12 +6049,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6034,7 +6064,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
+  <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -6049,7 +6079,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6067,16 +6097,20 @@
       <c r="C4" s="3">
         <v>46113</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
       <c r="H4" s="1">
         <v>20</v>
       </c>
       <c r="I4" s="5">
         <f>G4/H4</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -6092,13 +6126,13 @@
         <v>20</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <f t="shared" ref="I5:I33" si="0">G5/H5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <f t="shared" ref="C6:C33" si="1">C5+1</f>
         <v>46115</v>
       </c>
       <c r="D6" s="4"/>
@@ -6572,41 +6606,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46143</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1" t="e">
-        <f>AVERAGE(G4:G34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0</v>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D35" s="4">
+        <f>SUM(D4:D33)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="5">
+        <f>D35/31</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="1">
+        <f>AVERAGE(G4:G33)</f>
+        <v>12</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="5">
+        <f>AVERAGE(I4:I33)</f>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -6615,22 +6632,23 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+  <conditionalFormatting sqref="C4:C33">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+  <conditionalFormatting sqref="D4:D33">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
-      <formula>8</formula>
+  <conditionalFormatting sqref="G4:G33">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+      <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6651,7 +6669,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7342,17 +7360,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7378,7 +7396,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8006,17 +8024,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8042,7 +8060,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8722,6 +8740,733 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46114</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="21"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -8750,733 +9495,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46113</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
@@ -9494,7 +9512,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10164,17 +10182,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10200,7 +10218,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10897,17 +10915,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10933,7 +10951,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -11612,17 +11630,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -325,7 +325,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="44">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -358,16 +358,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -383,26 +373,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1155,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1722,17 +1692,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1757,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2457,17 +2427,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2496,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3211,17 +3181,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3247,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3938,17 +3908,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3974,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4683,17 +4653,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4720,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -5361,17 +5331,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6049,12 +6019,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6079,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6118,16 +6088,20 @@
         <f>C4+1</f>
         <v>46114</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1">
+        <v>12</v>
+      </c>
       <c r="H5" s="1">
         <v>20</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I33" si="0">G5/H5</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -6623,7 +6597,7 @@
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -6633,17 +6607,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6669,7 +6643,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7360,17 +7334,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7396,7 +7370,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8024,17 +7998,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8060,7 +8034,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8749,17 +8723,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8785,7 +8759,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9476,17 +9450,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9512,7 +9486,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10182,17 +10156,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10218,7 +10192,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10915,17 +10889,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10951,7 +10925,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -11630,17 +11604,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6109,16 +6109,20 @@
         <f t="shared" ref="C6:C33" si="1">C5+1</f>
         <v>46115</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>11</v>
+      </c>
       <c r="H6" s="1">
         <v>20</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -6126,16 +6130,20 @@
         <f t="shared" si="1"/>
         <v>46116</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>7</v>
+      </c>
       <c r="H7" s="1">
         <v>20</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -6592,12 +6600,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6643,7 +6651,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7370,7 +7378,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8034,7 +8042,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8759,7 +8767,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9486,7 +9494,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10192,7 +10200,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10925,7 +10933,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6151,16 +6151,20 @@
         <f t="shared" si="1"/>
         <v>46117</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
       <c r="H8" s="1">
         <v>20</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -6591,21 +6595,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>7.0000000000000007E-2</v>
+        <v>8.666666666666667E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6651,7 +6655,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7378,7 +7382,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8042,7 +8046,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8767,7 +8771,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9494,7 +9498,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10200,7 +10204,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10933,7 +10937,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6172,16 +6172,20 @@
         <f t="shared" si="1"/>
         <v>46118</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>12</v>
+      </c>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -6595,21 +6599,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>6.4516129032258063E-2</v>
+        <v>9.6774193548387094E-2</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.4</v>
+        <v>10.666666666666666</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>8.666666666666667E-2</v>
+        <v>0.10666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6655,7 +6659,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7382,7 +7386,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8046,7 +8050,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8771,7 +8775,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9498,7 +9502,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10204,7 +10208,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10937,7 +10941,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6193,16 +6193,20 @@
         <f t="shared" si="1"/>
         <v>46119</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>12</v>
+      </c>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
@@ -6608,12 +6612,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.666666666666666</v>
+        <v>10.857142857142858</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.10666666666666667</v>
+        <v>0.12666666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -6659,7 +6663,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7386,7 +7390,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8050,7 +8054,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8775,7 +8779,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9502,7 +9506,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10208,7 +10212,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10941,7 +10945,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6214,16 +6214,20 @@
         <f t="shared" si="1"/>
         <v>46120</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>14</v>
+      </c>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -6612,12 +6616,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.857142857142858</v>
+        <v>11.25</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.12666666666666668</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -6663,7 +6667,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7390,7 +7394,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8054,7 +8058,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8779,7 +8783,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9506,7 +9510,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10212,7 +10216,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10945,7 +10949,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6235,16 +6235,20 @@
         <f t="shared" si="1"/>
         <v>46121</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
@@ -6607,21 +6611,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>9.6774193548387094E-2</v>
+        <v>0.12903225806451613</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.25</v>
+        <v>11.222222222222221</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.15</v>
+        <v>0.16833333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -6667,7 +6671,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7394,7 +7398,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8058,7 +8062,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8783,7 +8787,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9510,7 +9514,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10216,7 +10220,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10949,7 +10953,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6256,16 +6256,20 @@
         <f t="shared" si="1"/>
         <v>46122</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
@@ -6273,16 +6277,20 @@
         <f t="shared" si="1"/>
         <v>46123</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
       <c r="H14" s="1">
         <v>20</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
@@ -6290,16 +6298,20 @@
         <f t="shared" si="1"/>
         <v>46124</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>9</v>
+      </c>
       <c r="H15" s="1">
         <v>20</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
@@ -6611,21 +6623,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.12903225806451613</v>
+        <v>0.19354838709677419</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.222222222222221</v>
+        <v>11.333333333333334</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.16833333333333333</v>
+        <v>0.22666666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -6671,7 +6683,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7398,7 +7410,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8062,7 +8074,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8787,7 +8799,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9514,7 +9526,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10220,7 +10232,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10953,7 +10965,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6319,16 +6319,20 @@
         <f t="shared" si="1"/>
         <v>46125</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>14</v>
+      </c>
       <c r="H16" s="1">
         <v>20</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
@@ -6632,12 +6636,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.333333333333334</v>
+        <v>11.538461538461538</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.22666666666666666</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -6683,7 +6687,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7410,7 +7414,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8074,7 +8078,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8799,7 +8803,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9526,7 +9530,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10232,7 +10236,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10965,7 +10969,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6340,16 +6340,20 @@
         <f t="shared" si="1"/>
         <v>46126</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>12</v>
+      </c>
       <c r="H17" s="1">
         <v>20</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
@@ -6627,21 +6631,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.19354838709677419</v>
+        <v>0.22580645161290322</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.538461538461538</v>
+        <v>11.571428571428571</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.25</v>
+        <v>0.26999999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -6687,7 +6691,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7414,7 +7418,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8078,7 +8082,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8803,7 +8807,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9530,7 +9534,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10236,7 +10240,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10969,7 +10973,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6361,16 +6361,20 @@
         <f t="shared" si="1"/>
         <v>46127</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
       <c r="H18" s="1">
         <v>20</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
@@ -6631,21 +6635,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.22580645161290322</v>
+        <v>0.25806451612903225</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.571428571428571</v>
+        <v>11.466666666666667</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.26999999999999996</v>
+        <v>0.28666666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -6691,7 +6695,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7418,7 +7422,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8082,7 +8086,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8807,7 +8811,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9534,7 +9538,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10240,7 +10244,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10973,7 +10977,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6382,16 +6382,20 @@
         <f t="shared" si="1"/>
         <v>46128</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>12</v>
+      </c>
       <c r="H19" s="1">
         <v>20</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.3">
@@ -6635,21 +6639,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.25806451612903225</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.466666666666667</v>
+        <v>11.5</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.28666666666666668</v>
+        <v>0.30666666666666664</v>
       </c>
     </row>
   </sheetData>
@@ -6695,7 +6699,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7422,7 +7426,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8086,7 +8090,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8811,7 +8815,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9538,7 +9542,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10244,7 +10248,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10977,7 +10981,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6403,16 +6403,20 @@
         <f t="shared" si="1"/>
         <v>46129</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>12</v>
+      </c>
       <c r="H20" s="1">
         <v>20</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.3">
@@ -6420,16 +6424,20 @@
         <f t="shared" si="1"/>
         <v>46130</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
       <c r="H21" s="1">
         <v>20</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
@@ -6437,16 +6445,20 @@
         <f t="shared" si="1"/>
         <v>46131</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
       <c r="H22" s="1">
         <v>20</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.3">
@@ -6639,21 +6651,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.29032258064516131</v>
+        <v>0.38709677419354838</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.5</v>
+        <v>11.315789473684211</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.30666666666666664</v>
+        <v>0.35833333333333328</v>
       </c>
     </row>
   </sheetData>
@@ -6699,7 +6711,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7426,7 +7438,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8090,7 +8102,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8815,7 +8827,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9542,7 +9554,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10248,7 +10260,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10981,7 +10993,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6466,16 +6466,20 @@
         <f t="shared" si="1"/>
         <v>46132</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
       <c r="H23" s="1">
         <v>20</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.3">
@@ -6651,21 +6655,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.38709677419354838</v>
+        <v>0.41935483870967744</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.315789473684211</v>
+        <v>11.3</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.35833333333333328</v>
+        <v>0.37666666666666665</v>
       </c>
     </row>
   </sheetData>
@@ -6711,7 +6715,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7438,7 +7442,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8102,7 +8106,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8827,7 +8831,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9554,7 +9558,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10260,7 +10264,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10993,7 +10997,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6487,16 +6487,20 @@
         <f t="shared" si="1"/>
         <v>46133</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
       <c r="H24" s="1">
         <v>20</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.3">
@@ -6504,16 +6508,20 @@
         <f t="shared" si="1"/>
         <v>46134</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>11</v>
+      </c>
       <c r="H25" s="1">
         <v>20</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.3">
@@ -6655,21 +6663,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.41935483870967744</v>
+        <v>0.45161290322580644</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.3</v>
+        <v>11.227272727272727</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.37666666666666665</v>
+        <v>0.41166666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -6715,7 +6723,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7442,7 +7450,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8106,7 +8114,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8831,7 +8839,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9558,7 +9566,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10264,7 +10272,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10997,7 +11005,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6529,16 +6529,20 @@
         <f t="shared" si="1"/>
         <v>46135</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>2</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>12</v>
+      </c>
       <c r="H26" s="1">
         <v>20</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.3">
@@ -6663,21 +6667,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.45161290322580644</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.227272727272727</v>
+        <v>11.260869565217391</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.41166666666666668</v>
+        <v>0.43166666666666664</v>
       </c>
     </row>
   </sheetData>
@@ -6723,7 +6727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7450,7 +7454,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8114,7 +8118,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8839,7 +8843,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9566,7 +9570,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10272,7 +10276,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -11005,7 +11009,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6550,16 +6550,20 @@
         <f t="shared" si="1"/>
         <v>46136</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>9</v>
+      </c>
       <c r="H27" s="1">
         <v>20</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
@@ -6567,16 +6571,20 @@
         <f t="shared" si="1"/>
         <v>46137</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
       <c r="H28" s="1">
         <v>20</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
@@ -6584,16 +6592,20 @@
         <f t="shared" si="1"/>
         <v>46138</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>11</v>
+      </c>
       <c r="H29" s="1">
         <v>20</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
@@ -6667,21 +6679,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.5161290322580645</v>
+        <v>0.58064516129032262</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.260869565217391</v>
+        <v>11.115384615384615</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.43166666666666664</v>
+        <v>0.48166666666666663</v>
       </c>
     </row>
   </sheetData>
@@ -6727,7 +6739,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7454,7 +7466,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8118,7 +8130,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8843,7 +8855,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9570,7 +9582,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10276,7 +10288,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -11009,7 +11021,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6613,16 +6613,20 @@
         <f t="shared" si="1"/>
         <v>46139</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>12</v>
+      </c>
       <c r="H30" s="1">
         <v>20</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
@@ -6688,12 +6692,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.115384615384615</v>
+        <v>11.148148148148149</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.48166666666666663</v>
+        <v>0.50166666666666659</v>
       </c>
     </row>
   </sheetData>
@@ -6739,7 +6743,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7466,7 +7470,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8130,7 +8134,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8855,7 +8859,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9582,7 +9586,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10288,7 +10292,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -11021,7 +11025,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6634,16 +6634,20 @@
         <f t="shared" si="1"/>
         <v>46140</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>12</v>
+      </c>
       <c r="H31" s="1">
         <v>20</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
@@ -6683,21 +6687,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E35" s="5">
         <f>D35/31</f>
-        <v>0.58064516129032262</v>
+        <v>0.64516129032258063</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.148148148148149</v>
+        <v>11.178571428571429</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.50166666666666659</v>
+        <v>0.52166666666666661</v>
       </c>
     </row>
   </sheetData>
@@ -6743,7 +6747,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7470,7 +7474,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8134,7 +8138,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8859,7 +8863,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9586,7 +9590,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10292,7 +10296,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -11025,7 +11029,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1125,7 +1125,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -1727,7 +1727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -2466,7 +2466,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3217,7 +3217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -3944,7 +3944,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -4690,7 +4690,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6049,7 +6049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -6655,16 +6655,20 @@
         <f t="shared" si="1"/>
         <v>46141</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1">
+        <v>11</v>
+      </c>
       <c r="H32" s="1">
         <v>20</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
@@ -6696,12 +6700,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.178571428571429</v>
+        <v>11.172413793103448</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.52166666666666661</v>
+        <v>0.53999999999999992</v>
       </c>
     </row>
   </sheetData>
@@ -6747,7 +6751,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -7474,7 +7478,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8138,7 +8142,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -8863,7 +8867,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -9590,7 +9594,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -10296,7 +10300,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">
@@ -11029,7 +11033,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="21" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -13,20 +13,21 @@
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
-    <sheet name="2026-04" sheetId="16" r:id="rId2"/>
-    <sheet name="2026-03" sheetId="15" r:id="rId3"/>
-    <sheet name="2026-02" sheetId="14" r:id="rId4"/>
-    <sheet name="2026-01" sheetId="13" r:id="rId5"/>
-    <sheet name="2025-12" sheetId="12" r:id="rId6"/>
-    <sheet name="2025-11" sheetId="11" r:id="rId7"/>
-    <sheet name="2025-10" sheetId="10" r:id="rId8"/>
-    <sheet name="2025-09" sheetId="9" r:id="rId9"/>
-    <sheet name="2025-08" sheetId="8" r:id="rId10"/>
-    <sheet name="2025-07" sheetId="7" r:id="rId11"/>
-    <sheet name="2025-06" sheetId="6" r:id="rId12"/>
-    <sheet name="2025-05" sheetId="5" r:id="rId13"/>
-    <sheet name="2025-04" sheetId="4" r:id="rId14"/>
-    <sheet name="2025-03" sheetId="1" r:id="rId15"/>
+    <sheet name="2026-05" sheetId="17" r:id="rId2"/>
+    <sheet name="2026-04" sheetId="16" r:id="rId3"/>
+    <sheet name="2026-03" sheetId="15" r:id="rId4"/>
+    <sheet name="2026-02" sheetId="14" r:id="rId5"/>
+    <sheet name="2026-01" sheetId="13" r:id="rId6"/>
+    <sheet name="2025-12" sheetId="12" r:id="rId7"/>
+    <sheet name="2025-11" sheetId="11" r:id="rId8"/>
+    <sheet name="2025-10" sheetId="10" r:id="rId9"/>
+    <sheet name="2025-09" sheetId="9" r:id="rId10"/>
+    <sheet name="2025-08" sheetId="8" r:id="rId11"/>
+    <sheet name="2025-07" sheetId="7" r:id="rId12"/>
+    <sheet name="2025-06" sheetId="6" r:id="rId13"/>
+    <sheet name="2025-05" sheetId="5" r:id="rId14"/>
+    <sheet name="2025-04" sheetId="4" r:id="rId15"/>
+    <sheet name="2025-03" sheetId="1" r:id="rId16"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -254,7 +255,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -321,11 +322,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="47">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1125,19 +1159,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -1692,17 +1726,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1711,6 +1745,721 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46148</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45901</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45902</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I33" si="0">G5/H5</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C33" si="1">C5+1</f>
+        <v>45903</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45904</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45905</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45906</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45907</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45908</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>13</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45909</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45910</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>9</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45911</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45912</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>9</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45913</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>7</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45914</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45915</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45916</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45917</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>11</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45918</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45919</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45920</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45921</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45922</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>11</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45923</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45924</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45925</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45926</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45927</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="13">
+        <v>4</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45928</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="13">
+        <v>8</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45929</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="13">
+        <v>7</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45930</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>4</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D35" s="4">
+        <f>SUM(D4:D33)</f>
+        <v>15</v>
+      </c>
+      <c r="E35" s="5">
+        <f>D35/30</f>
+        <v>0.5</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="1">
+        <f>AVERAGE(G4:G33)</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="5">
+        <f>AVERAGE(I4:I33)</f>
+        <v>0.41833333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C33">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D33">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G33">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+      <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1727,19 +2476,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -2418,6 +3167,760 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.44838709677419353</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46148</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
       </c>
     </row>
   </sheetData>
@@ -2446,761 +3949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46142</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3217,19 +3966,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3908,17 +4657,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3927,7 +4676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3944,19 +4693,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4653,17 +5402,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4673,7 +5422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4690,19 +5439,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5331,17 +6080,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5349,7 +6098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5361,16 +6110,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="22"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="F2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -6019,12 +6768,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6033,6 +6782,628 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46148</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46143</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46144</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>46145</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46146</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>12</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46147</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46148</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46149</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46150</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46151</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46152</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46153</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46154</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46155</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46156</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46157</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46158</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46159</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46160</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46161</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46162</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46163</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46164</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46165</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46166</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46167</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46168</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46169</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46170</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46171</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46172</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46173</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>4</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>11.2</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>9.0322580645161299E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6049,19 +7420,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6676,16 +8047,20 @@
         <f t="shared" si="1"/>
         <v>46142</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1">
+        <v>11</v>
+      </c>
       <c r="H33" s="1">
         <v>20</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
@@ -6700,12 +8075,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.172413793103448</v>
+        <v>11.166666666666666</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.53999999999999992</v>
+        <v>0.55833333333333335</v>
       </c>
     </row>
   </sheetData>
@@ -6715,17 +8090,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6734,7 +8109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6751,19 +8126,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7442,17 +8817,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7461,7 +8836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7478,19 +8853,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8106,17 +9481,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8125,7 +9500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8142,19 +9517,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8822,6 +10197,733 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46148</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -8850,734 +10952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46142</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9594,19 +10969,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10264,17 +11639,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10283,7 +11658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10300,19 +11675,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10997,736 +12372,21 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46142</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45901</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45902</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>9</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I33" si="0">G5/H5</f>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C33" si="1">C5+1</f>
-        <v>45903</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45904</v>
-      </c>
-      <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>11</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45905</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45906</v>
-      </c>
-      <c r="D9" s="4">
-        <v>2</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>8</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45907</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45908</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>13</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45909</v>
-      </c>
-      <c r="D12" s="4">
-        <v>2</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45910</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>9</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-      <c r="J13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45911</v>
-      </c>
-      <c r="D14" s="4">
-        <v>2</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>10</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45912</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>9</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45913</v>
-      </c>
-      <c r="D16" s="4">
-        <v>2</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>7</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45914</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45915</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45916</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45917</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>11</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45918</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45919</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45920</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45921</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>10</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45922</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>11</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45923</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45924</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45925</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45926</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45927</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="13">
-        <v>4</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45928</v>
-      </c>
-      <c r="D31" s="4">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="13">
-        <v>8</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45929</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="13">
-        <v>7</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45930</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>4</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D35" s="4">
-        <f>SUM(D4:D33)</f>
-        <v>15</v>
-      </c>
-      <c r="E35" s="5">
-        <f>D35/30</f>
-        <v>0.5</v>
-      </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="1">
-        <f>AVERAGE(G4:G33)</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="5">
-        <f>AVERAGE(I4:I33)</f>
-        <v>0.41833333333333333</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
-      <formula>7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -362,21 +362,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2440,17 +2440,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3167,760 +3167,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.44838709677419353</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46148</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
       </c>
     </row>
   </sheetData>
@@ -3949,6 +3195,760 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46149</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4657,17 +4657,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5402,17 +5402,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6080,17 +6080,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6768,12 +6768,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6921,16 +6921,20 @@
         <f t="shared" si="1"/>
         <v>46148</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>11</v>
+      </c>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -7361,21 +7365,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.12903225806451613</v>
+        <v>0.16129032258064516</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.2</v>
+        <v>11.166666666666666</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>9.0322580645161299E-2</v>
+        <v>0.10806451612903227</v>
       </c>
     </row>
   </sheetData>
@@ -7385,21 +7389,22 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7420,7 +7425,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8090,17 +8095,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8126,7 +8131,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8817,17 +8822,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8853,7 +8858,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9481,17 +9486,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9517,7 +9522,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10197,733 +10202,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46148</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -10952,6 +10230,733 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46149</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
@@ -10969,7 +10974,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11639,17 +11644,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11675,7 +11680,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -12372,17 +12377,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6942,16 +6942,20 @@
         <f t="shared" si="1"/>
         <v>46149</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>12</v>
+      </c>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
@@ -7365,21 +7369,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.16129032258064516</v>
+        <v>0.22580645161290322</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.166666666666666</v>
+        <v>11.285714285714286</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.10806451612903227</v>
+        <v>0.1274193548387097</v>
       </c>
     </row>
   </sheetData>
@@ -7425,7 +7429,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8131,7 +8135,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8858,7 +8862,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9522,7 +9526,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10247,7 +10251,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10974,7 +10978,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11680,7 +11684,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6963,16 +6963,20 @@
         <f t="shared" si="1"/>
         <v>46150</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -6980,16 +6984,20 @@
         <f t="shared" si="1"/>
         <v>46151</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>12</v>
+      </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
@@ -6997,7 +7005,9 @@
         <f t="shared" si="1"/>
         <v>46152</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="1"/>
@@ -7369,21 +7379,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.22580645161290322</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.285714285714286</v>
+        <v>11.222222222222221</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.1274193548387097</v>
+        <v>0.16290322580645164</v>
       </c>
     </row>
   </sheetData>
@@ -7429,7 +7439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8135,7 +8145,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8862,7 +8872,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9526,7 +9536,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10251,7 +10261,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10978,7 +10988,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11684,7 +11694,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7010,13 +7010,15 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>9</v>
+      </c>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
@@ -7388,12 +7390,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.222222222222221</v>
+        <v>11</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.16290322580645164</v>
+        <v>0.17741935483870971</v>
       </c>
     </row>
   </sheetData>
@@ -7439,7 +7441,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8145,7 +8147,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8872,7 +8874,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9536,7 +9538,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10261,7 +10263,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10988,7 +10990,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11694,7 +11696,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7026,16 +7026,20 @@
         <f t="shared" si="1"/>
         <v>46153</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>9</v>
+      </c>
       <c r="H14" s="1">
         <v>20</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
@@ -7390,12 +7394,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11</v>
+        <v>10.818181818181818</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.17741935483870971</v>
+        <v>0.19193548387096779</v>
       </c>
     </row>
   </sheetData>
@@ -7441,7 +7445,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8147,7 +8151,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8874,7 +8878,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9538,7 +9542,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10263,7 +10267,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10990,7 +10994,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11696,7 +11700,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7047,16 +7047,20 @@
         <f t="shared" si="1"/>
         <v>46154</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
       <c r="H15" s="1">
         <v>20</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
@@ -7385,21 +7389,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.29032258064516131</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.818181818181818</v>
+        <v>10.833333333333334</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.19193548387096779</v>
+        <v>0.20967741935483875</v>
       </c>
     </row>
   </sheetData>
@@ -7445,7 +7449,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8151,7 +8155,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8878,7 +8882,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9542,7 +9546,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10267,7 +10271,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10994,7 +10998,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11700,7 +11704,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7068,16 +7068,20 @@
         <f t="shared" si="1"/>
         <v>46155</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
       <c r="H16" s="1">
         <v>20</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
@@ -7398,12 +7402,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.833333333333334</v>
+        <v>10.76923076923077</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.20967741935483875</v>
+        <v>0.22580645161290325</v>
       </c>
     </row>
   </sheetData>
@@ -7449,7 +7453,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8155,7 +8159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8882,7 +8886,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9546,7 +9550,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10271,7 +10275,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10998,7 +11002,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11704,7 +11708,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7089,16 +7089,20 @@
         <f t="shared" si="1"/>
         <v>46156</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
       <c r="H17" s="1">
         <v>20</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
@@ -7393,21 +7397,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.35483870967741937</v>
+        <v>0.41935483870967744</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.76923076923077</v>
+        <v>10.785714285714286</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.22580645161290325</v>
+        <v>0.2435483870967742</v>
       </c>
     </row>
   </sheetData>
@@ -7453,7 +7457,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8159,7 +8163,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8886,7 +8890,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9550,7 +9554,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10275,7 +10279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11002,7 +11006,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11708,7 +11712,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7110,16 +7110,20 @@
         <f t="shared" si="1"/>
         <v>46157</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>11</v>
+      </c>
       <c r="H18" s="1">
         <v>20</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
@@ -7127,16 +7131,20 @@
         <f t="shared" si="1"/>
         <v>46158</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
       <c r="H19" s="1">
         <v>20</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.3">
@@ -7144,16 +7152,20 @@
         <f t="shared" si="1"/>
         <v>46159</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
       <c r="H20" s="1">
         <v>20</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.3">
@@ -7161,16 +7173,20 @@
         <f t="shared" si="1"/>
         <v>46160</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>12</v>
+      </c>
       <c r="H21" s="1">
         <v>20</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
@@ -7397,21 +7413,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.41935483870967744</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.785714285714286</v>
+        <v>10.777777777777779</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.2435483870967742</v>
+        <v>0.31290322580645163</v>
       </c>
     </row>
   </sheetData>
@@ -7457,7 +7473,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8163,7 +8179,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8890,7 +8906,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9554,7 +9570,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10279,7 +10295,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11006,7 +11022,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11712,7 +11728,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7194,16 +7194,20 @@
         <f t="shared" si="1"/>
         <v>46161</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>13</v>
+      </c>
       <c r="H22" s="1">
         <v>20</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.3">
@@ -7413,21 +7417,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.5161290322580645</v>
+        <v>0.58064516129032262</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.777777777777779</v>
+        <v>10.894736842105264</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.31290322580645163</v>
+        <v>0.33387096774193553</v>
       </c>
     </row>
   </sheetData>
@@ -7473,7 +7477,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8179,7 +8183,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8906,7 +8910,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9570,7 +9574,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10295,7 +10299,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11022,7 +11026,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11728,7 +11732,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7215,16 +7215,20 @@
         <f t="shared" si="1"/>
         <v>46162</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
       <c r="H23" s="1">
         <v>20</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.3">
@@ -7426,12 +7430,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.894736842105264</v>
+        <v>10.75</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.33387096774193553</v>
+        <v>0.34677419354838718</v>
       </c>
     </row>
   </sheetData>
@@ -7477,7 +7481,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8183,7 +8187,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8910,7 +8914,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9574,7 +9578,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10299,7 +10303,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11026,7 +11030,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11732,7 +11736,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7236,16 +7236,20 @@
         <f t="shared" si="1"/>
         <v>46163</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
       <c r="H24" s="1">
         <v>20</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.3">
@@ -7421,21 +7425,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.58064516129032262</v>
+        <v>0.64516129032258063</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.75</v>
+        <v>10.714285714285714</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.34677419354838718</v>
+        <v>0.36290322580645168</v>
       </c>
     </row>
   </sheetData>
@@ -7481,7 +7485,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8187,7 +8191,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8914,7 +8918,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9578,7 +9582,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10303,7 +10307,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11030,7 +11034,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11736,7 +11740,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7257,16 +7257,20 @@
         <f t="shared" si="1"/>
         <v>46164</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>11</v>
+      </c>
       <c r="H25" s="1">
         <v>20</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.3">
@@ -7274,16 +7278,20 @@
         <f t="shared" si="1"/>
         <v>46165</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
       <c r="H26" s="1">
         <v>20</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.3">
@@ -7291,16 +7299,20 @@
         <f t="shared" si="1"/>
         <v>46166</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>9</v>
+      </c>
       <c r="H27" s="1">
         <v>20</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
@@ -7308,16 +7320,20 @@
         <f t="shared" si="1"/>
         <v>46167</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>11</v>
+      </c>
       <c r="H28" s="1">
         <v>20</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
@@ -7425,21 +7441,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.64516129032258063</v>
+        <v>0.74193548387096775</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.714285714285714</v>
+        <v>10.68</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.36290322580645168</v>
+        <v>0.43064516129032271</v>
       </c>
     </row>
   </sheetData>
@@ -7485,7 +7501,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8191,7 +8207,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8918,7 +8934,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9582,7 +9598,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10307,7 +10323,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11034,7 +11050,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11740,7 +11756,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7341,16 +7341,20 @@
         <f t="shared" si="1"/>
         <v>46168</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>11</v>
+      </c>
       <c r="H29" s="1">
         <v>20</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
@@ -7441,21 +7445,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.74193548387096775</v>
+        <v>0.80645161290322576</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.68</v>
+        <v>10.692307692307692</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.43064516129032271</v>
+        <v>0.44838709677419369</v>
       </c>
     </row>
   </sheetData>
@@ -7501,7 +7505,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8207,7 +8211,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8934,7 +8938,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9598,7 +9602,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10323,7 +10327,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11050,7 +11054,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11756,7 +11760,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7362,16 +7362,20 @@
         <f t="shared" si="1"/>
         <v>46169</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
       <c r="H30" s="1">
         <v>20</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
@@ -7454,12 +7458,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.692307692307692</v>
+        <v>10.666666666666666</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.44838709677419369</v>
+        <v>0.4645161290322582</v>
       </c>
     </row>
   </sheetData>
@@ -7505,7 +7509,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8211,7 +8215,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8938,7 +8942,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9602,7 +9606,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10327,7 +10331,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11054,7 +11058,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11760,7 +11764,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1159,7 +1159,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -1761,7 +1761,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -2476,7 +2476,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3215,7 +3215,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -3966,7 +3966,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -4693,7 +4693,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -5439,7 +5439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -6798,7 +6798,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -7383,16 +7383,20 @@
         <f t="shared" si="1"/>
         <v>46170</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>11</v>
+      </c>
       <c r="H31" s="1">
         <v>20</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
@@ -7449,21 +7453,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.80645161290322576</v>
+        <v>0.87096774193548387</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.666666666666666</v>
+        <v>10.678571428571429</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.4645161290322582</v>
+        <v>0.48225806451612918</v>
       </c>
     </row>
   </sheetData>
@@ -7509,7 +7513,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8215,7 +8219,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -8942,7 +8946,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -9606,7 +9610,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -10331,7 +10335,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11058,7 +11062,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">
@@ -11764,7 +11768,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="22" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -9,25 +9,26 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="1"/>
+    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
-    <sheet name="2026-05" sheetId="17" r:id="rId2"/>
-    <sheet name="2026-04" sheetId="16" r:id="rId3"/>
-    <sheet name="2026-03" sheetId="15" r:id="rId4"/>
-    <sheet name="2026-02" sheetId="14" r:id="rId5"/>
-    <sheet name="2026-01" sheetId="13" r:id="rId6"/>
-    <sheet name="2025-12" sheetId="12" r:id="rId7"/>
-    <sheet name="2025-11" sheetId="11" r:id="rId8"/>
-    <sheet name="2025-10" sheetId="10" r:id="rId9"/>
-    <sheet name="2025-09" sheetId="9" r:id="rId10"/>
-    <sheet name="2025-08" sheetId="8" r:id="rId11"/>
-    <sheet name="2025-07" sheetId="7" r:id="rId12"/>
-    <sheet name="2025-06" sheetId="6" r:id="rId13"/>
-    <sheet name="2025-05" sheetId="5" r:id="rId14"/>
-    <sheet name="2025-04" sheetId="4" r:id="rId15"/>
-    <sheet name="2025-03" sheetId="1" r:id="rId16"/>
+    <sheet name="2026-06" sheetId="18" r:id="rId2"/>
+    <sheet name="2026-05" sheetId="17" r:id="rId3"/>
+    <sheet name="2026-04" sheetId="16" r:id="rId4"/>
+    <sheet name="2026-03" sheetId="15" r:id="rId5"/>
+    <sheet name="2026-02" sheetId="14" r:id="rId6"/>
+    <sheet name="2026-01" sheetId="13" r:id="rId7"/>
+    <sheet name="2025-12" sheetId="12" r:id="rId8"/>
+    <sheet name="2025-11" sheetId="11" r:id="rId9"/>
+    <sheet name="2025-10" sheetId="10" r:id="rId10"/>
+    <sheet name="2025-09" sheetId="9" r:id="rId11"/>
+    <sheet name="2025-08" sheetId="8" r:id="rId12"/>
+    <sheet name="2025-07" sheetId="7" r:id="rId13"/>
+    <sheet name="2025-06" sheetId="6" r:id="rId14"/>
+    <sheet name="2025-05" sheetId="5" r:id="rId15"/>
+    <sheet name="2025-04" sheetId="4" r:id="rId16"/>
+    <sheet name="2025-03" sheetId="1" r:id="rId17"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -78,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="23">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -165,6 +166,10 @@
   </si>
   <si>
     <t>뭐하고 있는거야???</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지연이 성적 때문에 많이 맛이 감.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -255,7 +260,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -325,11 +330,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="50">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1159,19 +1197,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -1726,17 +1764,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1745,6 +1783,739 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46173</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45931</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45932</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>4</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45933</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45934</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45935</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>5</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45936</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45937</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45938</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>7</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45939</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>9</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45940</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45941</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>6</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45942</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>12</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45943</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45944</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>6</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45945</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45946</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>4</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45947</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>8</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45948</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>8</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45949</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45950</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45951</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45952</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>4</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45953</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>8</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45954</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>4</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45955</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45956</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45957</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45958</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>8</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45959</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>8</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45960</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>4</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45961</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>10</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>17</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.54838709677419351</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>6.5483870967741939</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.32741935483870976</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1761,19 +2532,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -2440,17 +3211,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2459,7 +3230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2476,19 +3247,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3167,6 +3938,760 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.44838709677419353</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46173</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
       </c>
     </row>
   </sheetData>
@@ -3195,761 +4720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46171</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3966,19 +4737,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4657,17 +5428,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4676,7 +5447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4693,19 +5464,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5402,17 +6173,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5422,7 +6193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5439,19 +6210,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6080,17 +6851,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6098,7 +6869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6110,16 +6881,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="22"/>
+      <c r="C2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="23"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="F2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -6768,12 +7539,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6798,611 +7569,499 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
-        <v>46143</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
+        <v>45809</v>
+      </c>
+      <c r="D4" s="4"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>11</v>
-      </c>
+      <c r="G4" s="1"/>
       <c r="H4" s="1">
         <v>20</v>
       </c>
       <c r="I4" s="5">
         <f>G4/H4</f>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
-        <v>46144</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
+        <v>45810</v>
+      </c>
+      <c r="D5" s="4"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>11</v>
-      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="1">
         <v>20</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>46145</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
+        <v>45811</v>
+      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
+      <c r="G6" s="1"/>
       <c r="H6" s="1">
         <v>20</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>46146</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
+        <v>45812</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>12</v>
-      </c>
+      <c r="G7" s="1"/>
       <c r="H7" s="1">
         <v>20</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>46147</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
+        <v>45813</v>
+      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
+      <c r="G8" s="1"/>
       <c r="H8" s="1">
         <v>20</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
-        <v>46148</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
+        <v>45814</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>11</v>
-      </c>
+      <c r="G9" s="1"/>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
-        <v>46149</v>
-      </c>
-      <c r="D10" s="4">
-        <v>2</v>
-      </c>
+        <v>45815</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>12</v>
-      </c>
+      <c r="G10" s="1"/>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
-        <v>46150</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
+        <v>45816</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
+      <c r="G11" s="1"/>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
-        <v>46151</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
+        <v>45817</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>12</v>
-      </c>
+      <c r="G12" s="1"/>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
-        <v>46152</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
+        <v>45818</v>
+      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>9</v>
-      </c>
+      <c r="G13" s="1"/>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
-        <v>46153</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
+        <v>45819</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>9</v>
-      </c>
+      <c r="G14" s="1"/>
       <c r="H14" s="1">
         <v>20</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
-        <v>46154</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
+        <v>45820</v>
+      </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
+      <c r="G15" s="1"/>
       <c r="H15" s="1">
         <v>20</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
-        <v>46155</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
+        <v>45821</v>
+      </c>
+      <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
+      <c r="G16" s="1"/>
       <c r="H16" s="1">
         <v>20</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <f t="shared" si="1"/>
-        <v>46156</v>
-      </c>
-      <c r="D17" s="4">
-        <v>2</v>
-      </c>
+        <v>45822</v>
+      </c>
+      <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>11</v>
-      </c>
+      <c r="G17" s="1"/>
       <c r="H17" s="1">
         <v>20</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <f t="shared" si="1"/>
-        <v>46157</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
+        <v>45823</v>
+      </c>
+      <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>11</v>
-      </c>
+      <c r="G18" s="1"/>
       <c r="H18" s="1">
         <v>20</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <f t="shared" si="1"/>
-        <v>46158</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
+        <v>45824</v>
+      </c>
+      <c r="D19" s="4"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
+      <c r="G19" s="1"/>
       <c r="H19" s="1">
         <v>20</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <f t="shared" si="1"/>
-        <v>46159</v>
-      </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
+        <v>45825</v>
+      </c>
+      <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
+      <c r="G20" s="1"/>
       <c r="H20" s="1">
         <v>20</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <f t="shared" si="1"/>
-        <v>46160</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
+        <v>45826</v>
+      </c>
+      <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>12</v>
-      </c>
+      <c r="G21" s="1"/>
       <c r="H21" s="1">
         <v>20</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C22" s="3">
         <f t="shared" si="1"/>
-        <v>46161</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
+        <v>45827</v>
+      </c>
+      <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>13</v>
-      </c>
+      <c r="G22" s="1"/>
       <c r="H22" s="1">
         <v>20</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C23" s="3">
         <f t="shared" si="1"/>
-        <v>46162</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
+        <v>45828</v>
+      </c>
+      <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
+      <c r="G23" s="1"/>
       <c r="H23" s="1">
         <v>20</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <f t="shared" si="1"/>
-        <v>46163</v>
-      </c>
-      <c r="D24" s="4">
-        <v>2</v>
-      </c>
+        <v>45829</v>
+      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>10</v>
-      </c>
+      <c r="G24" s="1"/>
       <c r="H24" s="1">
         <v>20</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C25" s="3">
         <f t="shared" si="1"/>
-        <v>46164</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
+        <v>45830</v>
+      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>11</v>
-      </c>
+      <c r="G25" s="1"/>
       <c r="H25" s="1">
         <v>20</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C26" s="3">
         <f t="shared" si="1"/>
-        <v>46165</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
+        <v>45831</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
+      <c r="G26" s="1"/>
       <c r="H26" s="1">
         <v>20</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C27" s="3">
         <f t="shared" si="1"/>
-        <v>46166</v>
-      </c>
-      <c r="D27" s="4">
-        <v>2</v>
-      </c>
+        <v>45832</v>
+      </c>
+      <c r="D27" s="4"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>9</v>
-      </c>
+      <c r="G27" s="1"/>
       <c r="H27" s="1">
         <v>20</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C28" s="3">
         <f t="shared" si="1"/>
-        <v>46167</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
+        <v>45833</v>
+      </c>
+      <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>11</v>
-      </c>
+      <c r="G28" s="1"/>
       <c r="H28" s="1">
         <v>20</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C29" s="3">
         <f t="shared" si="1"/>
-        <v>46168</v>
-      </c>
-      <c r="D29" s="4">
-        <v>2</v>
-      </c>
+        <v>45834</v>
+      </c>
+      <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>11</v>
-      </c>
+      <c r="G29" s="1"/>
       <c r="H29" s="1">
         <v>20</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C30" s="3">
         <f t="shared" si="1"/>
-        <v>46169</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
+        <v>45835</v>
+      </c>
+      <c r="D30" s="4"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
+      <c r="G30" s="1"/>
       <c r="H30" s="1">
         <v>20</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C31" s="3">
         <f t="shared" si="1"/>
-        <v>46170</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
+        <v>45836</v>
+      </c>
+      <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>11</v>
-      </c>
+      <c r="G31" s="1"/>
       <c r="H31" s="1">
         <v>20</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C32" s="3">
         <f t="shared" si="1"/>
-        <v>46171</v>
+        <v>45837</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
@@ -7419,7 +8078,7 @@
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C33" s="3">
         <f t="shared" si="1"/>
-        <v>46172</v>
+        <v>45838</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
@@ -7436,7 +8095,7 @@
     <row r="34" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C34" s="3">
         <f t="shared" si="1"/>
-        <v>46173</v>
+        <v>45839</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
@@ -7453,21 +8112,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.87096774193548387</v>
+        <v>0</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="1">
+      <c r="G36" s="1" t="e">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.678571428571429</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.48225806451612918</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7477,17 +8136,742 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46173</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46143</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46144</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>46145</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46146</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>12</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46147</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46148</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>11</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46149</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>12</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46150</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46151</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>12</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46152</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>9</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46153</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>9</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46154</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46155</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46156</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46157</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>11</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46158</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46159</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46160</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>12</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46161</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>13</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46162</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46163</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46164</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>11</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46165</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46166</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>9</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46167</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>11</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46168</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>11</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46169</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46170</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>11</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46171</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>13</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46172</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>9</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46173</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.7</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.51774193548387115</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7496,7 +8880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7513,19 +8897,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8183,17 +9567,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8202,7 +9586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8219,19 +9603,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8910,17 +10294,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8929,7 +10313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8946,19 +10330,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9574,17 +10958,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9593,7 +10977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9610,19 +10994,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10290,6 +11674,733 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46173</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -10318,734 +12429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46171</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -11062,19 +12446,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11732,754 +13116,21 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46171</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45931</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45932</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>4</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45933</v>
-      </c>
-      <c r="D6" s="4">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45934</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>4</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45935</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>5</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45936</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>5</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45937</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>5</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45938</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>7</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45939</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>9</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45940</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>10</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45941</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>6</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45942</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>12</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45943</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>3</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45944</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>6</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45945</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45946</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>4</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45947</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>8</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45948</v>
-      </c>
-      <c r="D21" s="4">
-        <v>2</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>8</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45949</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>14</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45950</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45951</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>5</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45952</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>4</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45953</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>8</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45954</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>4</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45955</v>
-      </c>
-      <c r="D28" s="4">
-        <v>2</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>10</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45956</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45957</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>2</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45958</v>
-      </c>
-      <c r="D31" s="4">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>8</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45959</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>8</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45960</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>4</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45961</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>10</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>17</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.54838709677419351</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>6.5483870967741939</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.32741935483870976</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="2"/>
+    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885"/>
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
@@ -370,21 +370,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1197,7 +1197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -1213,7 +1213,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="3"/>
@@ -1230,7 +1230,7 @@
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
-        <v>45749</v>
+        <v>46114</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="3"/>
@@ -1247,7 +1247,7 @@
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45750</v>
+        <v>46115</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="3"/>
@@ -1264,7 +1264,7 @@
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>45751</v>
+        <v>46116</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="3"/>
@@ -1281,7 +1281,7 @@
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>45752</v>
+        <v>46117</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="3"/>
@@ -1298,7 +1298,7 @@
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
-        <v>45753</v>
+        <v>46118</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="3"/>
@@ -1315,7 +1315,7 @@
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
-        <v>45754</v>
+        <v>46119</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
@@ -1332,7 +1332,7 @@
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
-        <v>45755</v>
+        <v>46120</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
@@ -1349,7 +1349,7 @@
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
-        <v>45756</v>
+        <v>46121</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
@@ -1366,7 +1366,7 @@
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
-        <v>45757</v>
+        <v>46122</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="3"/>
@@ -1383,7 +1383,7 @@
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
-        <v>45758</v>
+        <v>46123</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
@@ -1400,7 +1400,7 @@
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
-        <v>45759</v>
+        <v>46124</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
@@ -1417,7 +1417,7 @@
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
-        <v>45760</v>
+        <v>46125</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
@@ -1434,7 +1434,7 @@
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <f t="shared" si="1"/>
-        <v>45761</v>
+        <v>46126</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
@@ -1451,7 +1451,7 @@
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <f t="shared" si="1"/>
-        <v>45762</v>
+        <v>46127</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
@@ -1468,7 +1468,7 @@
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <f t="shared" si="1"/>
-        <v>45763</v>
+        <v>46128</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="3"/>
@@ -1485,7 +1485,7 @@
     <row r="20" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <f t="shared" si="1"/>
-        <v>45764</v>
+        <v>46129</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
@@ -1502,7 +1502,7 @@
     <row r="21" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <f t="shared" si="1"/>
-        <v>45765</v>
+        <v>46130</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
@@ -1519,7 +1519,7 @@
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C22" s="3">
         <f t="shared" si="1"/>
-        <v>45766</v>
+        <v>46131</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
@@ -1536,7 +1536,7 @@
     <row r="23" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C23" s="3">
         <f t="shared" si="1"/>
-        <v>45767</v>
+        <v>46132</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
@@ -1553,7 +1553,7 @@
     <row r="24" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <f t="shared" si="1"/>
-        <v>45768</v>
+        <v>46133</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
@@ -1570,7 +1570,7 @@
     <row r="25" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C25" s="3">
         <f t="shared" si="1"/>
-        <v>45769</v>
+        <v>46134</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
@@ -1587,7 +1587,7 @@
     <row r="26" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C26" s="3">
         <f t="shared" si="1"/>
-        <v>45770</v>
+        <v>46135</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
@@ -1604,7 +1604,7 @@
     <row r="27" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C27" s="3">
         <f t="shared" si="1"/>
-        <v>45771</v>
+        <v>46136</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="3"/>
@@ -1621,7 +1621,7 @@
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C28" s="3">
         <f t="shared" si="1"/>
-        <v>45772</v>
+        <v>46137</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
@@ -1638,7 +1638,7 @@
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C29" s="3">
         <f t="shared" si="1"/>
-        <v>45773</v>
+        <v>46138</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
@@ -1655,7 +1655,7 @@
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C30" s="3">
         <f t="shared" si="1"/>
-        <v>45774</v>
+        <v>46139</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="3"/>
@@ -1672,7 +1672,7 @@
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C31" s="3">
         <f t="shared" si="1"/>
-        <v>45775</v>
+        <v>46140</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
@@ -1689,7 +1689,7 @@
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C32" s="3">
         <f t="shared" si="1"/>
-        <v>45776</v>
+        <v>46141</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
@@ -1706,7 +1706,7 @@
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C33" s="3">
         <f t="shared" si="1"/>
-        <v>45777</v>
+        <v>46142</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
@@ -1723,7 +1723,7 @@
     <row r="34" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C34" s="3">
         <f t="shared" si="1"/>
-        <v>45778</v>
+        <v>46143</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
@@ -1799,7 +1799,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -2496,17 +2496,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2532,7 +2532,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3211,17 +3211,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3247,7 +3247,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3938,760 +3938,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.44838709677419353</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46173</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
       </c>
     </row>
   </sheetData>
@@ -4720,6 +3966,760 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46174</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
@@ -4737,7 +4737,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -5428,17 +5428,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5464,7 +5464,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6173,17 +6173,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6210,7 +6210,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6851,17 +6851,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7539,12 +7539,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7569,7 +7569,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7585,7 +7585,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
-        <v>45809</v>
+        <v>46174</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="3"/>
@@ -7602,7 +7602,7 @@
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
-        <v>45810</v>
+        <v>46175</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="3"/>
@@ -7619,7 +7619,7 @@
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45811</v>
+        <v>46176</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="3"/>
@@ -7636,7 +7636,7 @@
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>45812</v>
+        <v>46177</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="3"/>
@@ -7653,7 +7653,7 @@
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>45813</v>
+        <v>46178</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="3"/>
@@ -7670,7 +7670,7 @@
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
-        <v>45814</v>
+        <v>46179</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="3"/>
@@ -7687,7 +7687,7 @@
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
-        <v>45815</v>
+        <v>46180</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
@@ -7704,7 +7704,7 @@
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
-        <v>45816</v>
+        <v>46181</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
@@ -7721,7 +7721,7 @@
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
-        <v>45817</v>
+        <v>46182</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
@@ -7738,7 +7738,7 @@
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
-        <v>45818</v>
+        <v>46183</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="3"/>
@@ -7755,7 +7755,7 @@
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
-        <v>45819</v>
+        <v>46184</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
@@ -7772,7 +7772,7 @@
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
-        <v>45820</v>
+        <v>46185</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
@@ -7789,7 +7789,7 @@
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
-        <v>45821</v>
+        <v>46186</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
@@ -7806,7 +7806,7 @@
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <f t="shared" si="1"/>
-        <v>45822</v>
+        <v>46187</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
@@ -7823,7 +7823,7 @@
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <f t="shared" si="1"/>
-        <v>45823</v>
+        <v>46188</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
@@ -7840,7 +7840,7 @@
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <f t="shared" si="1"/>
-        <v>45824</v>
+        <v>46189</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="3"/>
@@ -7857,7 +7857,7 @@
     <row r="20" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <f t="shared" si="1"/>
-        <v>45825</v>
+        <v>46190</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
@@ -7874,7 +7874,7 @@
     <row r="21" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <f t="shared" si="1"/>
-        <v>45826</v>
+        <v>46191</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
@@ -7891,7 +7891,7 @@
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C22" s="3">
         <f t="shared" si="1"/>
-        <v>45827</v>
+        <v>46192</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
@@ -7908,7 +7908,7 @@
     <row r="23" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C23" s="3">
         <f t="shared" si="1"/>
-        <v>45828</v>
+        <v>46193</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
@@ -7925,7 +7925,7 @@
     <row r="24" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <f t="shared" si="1"/>
-        <v>45829</v>
+        <v>46194</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
@@ -7942,7 +7942,7 @@
     <row r="25" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C25" s="3">
         <f t="shared" si="1"/>
-        <v>45830</v>
+        <v>46195</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
@@ -7959,7 +7959,7 @@
     <row r="26" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C26" s="3">
         <f t="shared" si="1"/>
-        <v>45831</v>
+        <v>46196</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
@@ -7976,7 +7976,7 @@
     <row r="27" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C27" s="3">
         <f t="shared" si="1"/>
-        <v>45832</v>
+        <v>46197</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="3"/>
@@ -7993,7 +7993,7 @@
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C28" s="3">
         <f t="shared" si="1"/>
-        <v>45833</v>
+        <v>46198</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
@@ -8010,7 +8010,7 @@
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C29" s="3">
         <f t="shared" si="1"/>
-        <v>45834</v>
+        <v>46199</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
@@ -8027,7 +8027,7 @@
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C30" s="3">
         <f t="shared" si="1"/>
-        <v>45835</v>
+        <v>46200</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="3"/>
@@ -8044,7 +8044,7 @@
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C31" s="3">
         <f t="shared" si="1"/>
-        <v>45836</v>
+        <v>46201</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
@@ -8061,7 +8061,7 @@
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C32" s="3">
         <f t="shared" si="1"/>
-        <v>45837</v>
+        <v>46202</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
@@ -8078,7 +8078,7 @@
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C33" s="3">
         <f t="shared" si="1"/>
-        <v>45838</v>
+        <v>46203</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
@@ -8095,7 +8095,7 @@
     <row r="34" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C34" s="3">
         <f t="shared" si="1"/>
-        <v>45839</v>
+        <v>46204</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
@@ -8127,731 +8127,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46173</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>46143</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>11</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>46144</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>11</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>46145</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>46146</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>12</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>46147</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>46148</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>11</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>46149</v>
-      </c>
-      <c r="D10" s="4">
-        <v>2</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>12</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>46150</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46151</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>12</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46152</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>9</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46153</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>9</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46154</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46155</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46156</v>
-      </c>
-      <c r="D17" s="4">
-        <v>2</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>11</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46157</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>11</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46158</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46159</v>
-      </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46160</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>12</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46161</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>13</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46162</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46163</v>
-      </c>
-      <c r="D24" s="4">
-        <v>2</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>10</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46164</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>11</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46165</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46166</v>
-      </c>
-      <c r="D27" s="4">
-        <v>2</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>9</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46167</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>11</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46168</v>
-      </c>
-      <c r="D29" s="4">
-        <v>2</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>11</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46169</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46170</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>11</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46171</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>13</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-      <c r="J32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46172</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>9</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46173</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.7</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.51774193548387115</v>
       </c>
     </row>
   </sheetData>
@@ -8880,6 +8155,736 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46174</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46143</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46144</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>46145</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46146</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>12</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46147</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46148</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>11</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46149</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>12</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46150</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46151</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>12</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46152</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>9</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46153</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>9</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46154</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46155</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46156</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46157</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>11</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46158</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46159</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46160</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>12</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46161</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>13</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46162</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46163</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46164</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>11</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46165</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46166</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>9</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46167</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>11</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46168</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>11</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46169</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46170</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>11</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46171</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>13</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46172</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>9</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46173</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>28</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.90322580645161288</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.709677419354838</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.53548387096774208</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
@@ -8897,7 +8902,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -9567,17 +9572,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9603,7 +9608,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10294,17 +10299,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10330,7 +10335,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10958,17 +10963,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10994,7 +10999,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11674,733 +11679,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46173</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -12429,6 +11707,733 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46174</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
@@ -12446,7 +12451,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -13116,17 +13121,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885"/>
+    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
@@ -1197,7 +1197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -1799,7 +1799,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -2532,7 +2532,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3247,7 +3247,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3986,7 +3986,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -4737,7 +4737,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -5464,7 +5464,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6210,7 +6210,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7569,7 +7569,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7587,16 +7587,20 @@
       <c r="C4" s="3">
         <v>46174</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
       <c r="H4" s="1">
         <v>20</v>
       </c>
       <c r="I4" s="5">
         <f>G4/H4</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -8119,14 +8123,14 @@
         <v>0</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="1" t="e">
+      <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>#DIV/0!</v>
+        <v>10</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0</v>
+        <v>1.6129032258064516E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8172,7 +8176,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -8902,7 +8906,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -9608,7 +9612,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10335,7 +10339,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10999,7 +11003,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11724,7 +11728,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -12451,7 +12455,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1197,7 +1197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -1799,7 +1799,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -2532,7 +2532,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3247,7 +3247,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3986,7 +3986,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -4737,7 +4737,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -5464,7 +5464,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6210,7 +6210,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7569,7 +7569,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7608,16 +7608,20 @@
         <f>C4+1</f>
         <v>46175</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
       <c r="H5" s="1">
         <v>20</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -7625,16 +7629,20 @@
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46176</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>9</v>
+      </c>
       <c r="H6" s="1">
         <v>20</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -8116,21 +8124,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0</v>
+        <v>9.6774193548387094E-2</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>1.6129032258064516E-2</v>
+        <v>4.6774193548387098E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8176,7 +8184,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -8906,7 +8914,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -9612,7 +9620,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10339,7 +10347,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11003,7 +11011,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11728,7 +11736,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -12455,7 +12463,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1197,7 +1197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -1799,7 +1799,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -2532,7 +2532,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3247,7 +3247,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3986,7 +3986,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -4737,7 +4737,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -5464,7 +5464,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6210,7 +6210,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7569,7 +7569,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7650,16 +7650,20 @@
         <f t="shared" si="1"/>
         <v>46177</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>11</v>
+      </c>
       <c r="H7" s="1">
         <v>20</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -8124,21 +8128,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>9.6774193548387094E-2</v>
+        <v>0.12903225806451613</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9.6666666666666661</v>
+        <v>10</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>4.6774193548387098E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8184,7 +8188,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -8914,7 +8918,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -9620,7 +9624,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10347,7 +10351,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11011,7 +11015,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11736,7 +11740,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -12463,7 +12467,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1197,7 +1197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -1799,7 +1799,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -2532,7 +2532,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3247,7 +3247,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3986,7 +3986,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -4737,7 +4737,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -5464,7 +5464,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6210,7 +6210,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7569,7 +7569,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7671,16 +7671,20 @@
         <f t="shared" si="1"/>
         <v>46178</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
       <c r="H8" s="1">
         <v>20</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -7688,16 +7692,20 @@
         <f t="shared" si="1"/>
         <v>46179</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>12</v>
+      </c>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -8128,21 +8136,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.12903225806451613</v>
+        <v>0.16129032258064516</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10</v>
+        <v>10.333333333333334</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>6.4516129032258063E-2</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -8188,7 +8196,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -8918,7 +8926,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -9624,7 +9632,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10351,7 +10359,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11015,7 +11023,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11740,7 +11748,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -12467,7 +12475,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,6 +170,10 @@
   </si>
   <si>
     <t>지연이 성적 때문에 많이 맛이 감.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 타임 더 뒤로 미뤄야 할 거 같다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1197,7 +1201,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -1799,7 +1803,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -2532,7 +2536,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3247,7 +3251,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3986,7 +3990,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -4737,7 +4741,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -5464,7 +5468,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6210,7 +6214,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7554,22 +7558,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
+  <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7583,7 +7587,7 @@
       <c r="H3" s="23"/>
       <c r="I3" s="23"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46174</v>
       </c>
@@ -7603,7 +7607,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46175</v>
@@ -7624,7 +7628,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46176</v>
@@ -7645,7 +7649,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46177</v>
@@ -7666,7 +7670,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46178</v>
@@ -7687,7 +7691,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46179</v>
@@ -7708,24 +7712,28 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46180</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>12</v>
+      </c>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46181</v>
@@ -7741,8 +7749,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46182</v>
@@ -7759,7 +7770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46183</v>
@@ -7776,7 +7787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46184</v>
@@ -7793,7 +7804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46185</v>
@@ -7810,7 +7821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46186</v>
@@ -8136,21 +8147,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.16129032258064516</v>
+        <v>0.22580645161290322</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.333333333333334</v>
+        <v>10.571428571428571</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.1</v>
+        <v>0.11935483870967742</v>
       </c>
     </row>
   </sheetData>
@@ -8196,7 +8207,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -8926,7 +8937,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -9632,7 +9643,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10359,7 +10370,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11023,7 +11034,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11748,7 +11759,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -12475,7 +12486,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1201,7 +1201,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -1803,7 +1803,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -2536,7 +2536,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3251,7 +3251,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3990,7 +3990,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -4741,7 +4741,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -5468,7 +5468,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6214,7 +6214,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7573,7 +7573,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7738,16 +7738,20 @@
         <f t="shared" si="1"/>
         <v>46181</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J11" t="s">
         <v>23</v>
@@ -8156,12 +8160,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.571428571428571</v>
+        <v>10.375</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.11935483870967742</v>
+        <v>0.13387096774193549</v>
       </c>
     </row>
   </sheetData>
@@ -8207,7 +8211,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -8937,7 +8941,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -9643,7 +9647,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10370,7 +10374,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11034,7 +11038,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11759,7 +11763,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -12486,7 +12490,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1201,7 +1201,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -1803,7 +1803,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -2536,7 +2536,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3251,7 +3251,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3990,7 +3990,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -4741,7 +4741,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -5468,7 +5468,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6214,7 +6214,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7573,7 +7573,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7762,16 +7762,20 @@
         <f t="shared" si="1"/>
         <v>46182</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
@@ -8151,21 +8155,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.22580645161290322</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.375</v>
+        <v>10.333333333333334</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.13387096774193549</v>
+        <v>0.15000000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -8211,7 +8215,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -8941,7 +8945,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -9647,7 +9651,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10374,7 +10378,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11038,7 +11042,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11763,7 +11767,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -12490,7 +12494,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -264,7 +264,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -336,6 +336,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1201,7 +1204,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -1803,7 +1806,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -2536,7 +2539,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3251,7 +3254,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -3990,7 +3993,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -4741,7 +4744,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -5468,7 +5471,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -6214,7 +6217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7573,7 +7576,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -7783,16 +7786,20 @@
         <f t="shared" si="1"/>
         <v>46183</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
@@ -8164,12 +8171,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.333333333333334</v>
+        <v>10.3</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.15000000000000002</v>
+        <v>0.16612903225806452</v>
       </c>
     </row>
   </sheetData>
@@ -8215,7 +8222,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -8607,7 +8614,7 @@
       </c>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
+      <c r="C22" s="24">
         <f t="shared" si="1"/>
         <v>46161</v>
       </c>
@@ -8817,7 +8824,7 @@
       </c>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
+      <c r="C32" s="24">
         <f t="shared" si="1"/>
         <v>46171</v>
       </c>
@@ -8945,7 +8952,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -9651,7 +9658,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -10378,7 +10385,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11042,7 +11049,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -11767,7 +11774,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">
@@ -12494,7 +12501,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="23" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -334,11 +334,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1204,19 +1204,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -1806,19 +1806,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -2539,19 +2539,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3254,19 +3254,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3993,19 +3993,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4744,19 +4744,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5471,19 +5471,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6217,19 +6217,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6888,16 +6888,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="23"/>
+      <c r="C2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="24"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="F2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -7576,19 +7576,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7807,16 +7807,20 @@
         <f t="shared" si="1"/>
         <v>46184</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>10</v>
+      </c>
       <c r="H14" s="1">
         <v>20</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
@@ -8162,21 +8166,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.29032258064516131</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.3</v>
+        <v>10.272727272727273</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.16612903225806452</v>
+        <v>0.18225806451612905</v>
       </c>
     </row>
   </sheetData>
@@ -8222,19 +8226,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8614,7 +8618,7 @@
       </c>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="24">
+      <c r="C22" s="23">
         <f t="shared" si="1"/>
         <v>46161</v>
       </c>
@@ -8824,7 +8828,7 @@
       </c>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="24">
+      <c r="C32" s="23">
         <f t="shared" si="1"/>
         <v>46171</v>
       </c>
@@ -8952,19 +8956,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9658,19 +9662,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10385,19 +10389,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11049,19 +11053,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11774,19 +11778,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -12501,19 +12505,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="D3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1204,7 +1204,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1806,7 +1806,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2539,7 +2539,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3254,7 +3254,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3993,7 +3993,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4744,7 +4744,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5471,7 +5471,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6217,7 +6217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7561,7 +7561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J36"/>
+  <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -7576,7 +7576,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7627,13 +7627,13 @@
         <v>20</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <f t="shared" ref="I5:I33" si="0">G5/H5</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <f t="shared" ref="C6:C33" si="1">C5+1</f>
         <v>46176</v>
       </c>
       <c r="D6" s="4">
@@ -7828,16 +7828,20 @@
         <f t="shared" si="1"/>
         <v>46185</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
       <c r="H15" s="1">
         <v>20</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
@@ -7845,16 +7849,20 @@
         <f t="shared" si="1"/>
         <v>46186</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>11</v>
+      </c>
       <c r="H16" s="1">
         <v>20</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
@@ -7862,16 +7870,20 @@
         <f t="shared" si="1"/>
         <v>46187</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
       <c r="H17" s="1">
         <v>20</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
@@ -8146,41 +8158,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46204</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>11</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.35483870967741937</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.272727272727273</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.18225806451612905</v>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D35" s="4">
+        <f>SUM(D4:D33)</f>
+        <v>14</v>
+      </c>
+      <c r="E35" s="5">
+        <f>D35/30</f>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="1">
+        <f>AVERAGE(G4:G33)</f>
+        <v>10.357142857142858</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="5">
+        <f>AVERAGE(I4:I33)</f>
+        <v>0.24166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -8189,17 +8184,17 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
+  <conditionalFormatting sqref="C4:C33">
     <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
+  <conditionalFormatting sqref="D4:D33">
     <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
+  <conditionalFormatting sqref="G4:G33">
     <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
@@ -8226,7 +8221,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8956,7 +8951,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9605,8 +9600,8 @@
         <v>20</v>
       </c>
       <c r="E35" s="5">
-        <f>D35/31</f>
-        <v>0.64516129032258063</v>
+        <f>D35/30</f>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
@@ -9662,7 +9657,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10389,7 +10384,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11053,7 +11048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11778,7 +11773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12505,7 +12500,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1204,7 +1204,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1806,7 +1806,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2539,7 +2539,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3254,7 +3254,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3993,7 +3993,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4744,7 +4744,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5471,7 +5471,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6217,7 +6217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7576,7 +7576,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7891,16 +7891,20 @@
         <f t="shared" si="1"/>
         <v>46188</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>9</v>
+      </c>
       <c r="H18" s="1">
         <v>20</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
@@ -8170,12 +8174,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.357142857142858</v>
+        <v>10.266666666666667</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.24166666666666667</v>
+        <v>0.25666666666666665</v>
       </c>
     </row>
   </sheetData>
@@ -8221,7 +8225,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8951,7 +8955,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9657,7 +9661,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10384,7 +10388,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11048,7 +11052,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11773,7 +11777,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12500,7 +12504,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1204,7 +1204,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1806,7 +1806,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2539,7 +2539,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3254,7 +3254,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3993,7 +3993,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4744,7 +4744,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5471,7 +5471,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6217,7 +6217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7576,7 +7576,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7912,16 +7912,20 @@
         <f t="shared" si="1"/>
         <v>46189</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>2</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
       <c r="H19" s="1">
         <v>20</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.3">
@@ -8165,21 +8169,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.46666666666666667</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.266666666666667</v>
+        <v>10.25</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.25666666666666665</v>
+        <v>0.27333333333333332</v>
       </c>
     </row>
   </sheetData>
@@ -8225,7 +8229,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8955,7 +8959,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9661,7 +9665,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10388,7 +10392,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11052,7 +11056,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11777,7 +11781,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12504,7 +12508,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1204,7 +1204,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1806,7 +1806,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2539,7 +2539,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3254,7 +3254,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3993,7 +3993,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4744,7 +4744,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5471,7 +5471,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6217,7 +6217,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7576,7 +7576,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7933,16 +7933,20 @@
         <f t="shared" si="1"/>
         <v>46190</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
       <c r="H20" s="1">
         <v>20</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.3">
@@ -8178,12 +8182,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.25</v>
+        <v>10.235294117647058</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.27333333333333332</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -8229,7 +8233,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8959,7 +8963,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9665,7 +9669,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10392,7 +10396,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11056,7 +11060,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11781,7 +11785,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12508,7 +12512,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="25">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -174,6 +174,10 @@
   </si>
   <si>
     <t>한 타임 더 뒤로 미뤄야 할 거 같다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침 다짐 실패, 희정 &amp; 회사?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1204,7 +1208,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1806,7 +1810,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2539,7 +2543,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3254,7 +3258,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3993,7 +3997,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4744,7 +4748,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5471,7 +5475,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6217,7 +6221,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7576,7 +7580,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7865,7 +7869,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <f t="shared" si="1"/>
         <v>46187</v>
@@ -7886,7 +7890,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <f t="shared" si="1"/>
         <v>46188</v>
@@ -7907,7 +7911,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <f t="shared" si="1"/>
         <v>46189</v>
@@ -7928,7 +7932,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <f t="shared" si="1"/>
         <v>46190</v>
@@ -7949,24 +7953,31 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <f t="shared" si="1"/>
         <v>46191</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>13</v>
+      </c>
       <c r="H21" s="1">
         <v>20</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+        <v>0.65</v>
+      </c>
+      <c r="J21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C22" s="3">
         <f t="shared" si="1"/>
         <v>46192</v>
@@ -7983,7 +7994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C23" s="3">
         <f t="shared" si="1"/>
         <v>46193</v>
@@ -8000,7 +8011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <f t="shared" si="1"/>
         <v>46194</v>
@@ -8017,7 +8028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C25" s="3">
         <f t="shared" si="1"/>
         <v>46195</v>
@@ -8034,7 +8045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C26" s="3">
         <f t="shared" si="1"/>
         <v>46196</v>
@@ -8051,7 +8062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C27" s="3">
         <f t="shared" si="1"/>
         <v>46197</v>
@@ -8068,7 +8079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C28" s="3">
         <f t="shared" si="1"/>
         <v>46198</v>
@@ -8085,7 +8096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C29" s="3">
         <f t="shared" si="1"/>
         <v>46199</v>
@@ -8102,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C30" s="3">
         <f t="shared" si="1"/>
         <v>46200</v>
@@ -8119,7 +8130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C31" s="3">
         <f t="shared" si="1"/>
         <v>46201</v>
@@ -8136,7 +8147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C32" s="3">
         <f t="shared" si="1"/>
         <v>46202</v>
@@ -8182,12 +8193,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.235294117647058</v>
+        <v>10.388888888888889</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.28999999999999998</v>
+        <v>0.31166666666666665</v>
       </c>
     </row>
   </sheetData>
@@ -8233,7 +8244,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8963,7 +8974,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9669,7 +9680,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10396,7 +10407,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11060,7 +11071,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11785,7 +11796,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12512,7 +12523,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -177,7 +177,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아침 다짐 실패, 희정 &amp; 회사?</t>
+    <t>아침 다짐 실패, 희정 &amp; 회사? -&gt; 다시 마음 잡아야지!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1208,7 +1208,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1810,7 +1810,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2543,7 +2543,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3258,7 +3258,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3997,7 +3997,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4748,7 +4748,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5475,7 +5475,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6221,7 +6221,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7580,7 +7580,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7982,16 +7982,20 @@
         <f t="shared" si="1"/>
         <v>46192</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>11</v>
+      </c>
       <c r="H22" s="1">
         <v>20</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.3">
@@ -7999,16 +8003,20 @@
         <f t="shared" si="1"/>
         <v>46193</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>10</v>
+      </c>
       <c r="H23" s="1">
         <v>20</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.3">
@@ -8016,16 +8024,20 @@
         <f t="shared" si="1"/>
         <v>46194</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
       <c r="H24" s="1">
         <v>20</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.3">
@@ -8184,21 +8196,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.53333333333333333</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.388888888888889</v>
+        <v>10.380952380952381</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.31166666666666665</v>
+        <v>0.36333333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -8244,7 +8256,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8974,7 +8986,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9680,7 +9692,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10407,7 +10419,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11071,7 +11083,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11796,7 +11808,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12523,7 +12535,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1208,7 +1208,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1810,7 +1810,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2543,7 +2543,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3258,7 +3258,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3997,7 +3997,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4748,7 +4748,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5475,7 +5475,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6221,7 +6221,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7580,7 +7580,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8045,16 +8045,20 @@
         <f t="shared" si="1"/>
         <v>46195</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>10</v>
+      </c>
       <c r="H25" s="1">
         <v>20</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.3">
@@ -8205,12 +8209,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.380952380952381</v>
+        <v>10.363636363636363</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.36333333333333334</v>
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -8256,7 +8260,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8986,7 +8990,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9692,7 +9696,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10419,7 +10423,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11083,7 +11087,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11808,7 +11812,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12535,7 +12539,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="26">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -178,6 +178,10 @@
   </si>
   <si>
     <t>아침 다짐 실패, 희정 &amp; 회사? -&gt; 다시 마음 잡아야지!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업무 스트레스?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1208,7 +1212,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1810,7 +1814,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2543,7 +2547,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3258,7 +3262,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3997,7 +4001,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4748,7 +4752,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5475,7 +5479,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6221,7 +6225,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7580,7 +7584,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8066,16 +8070,23 @@
         <f t="shared" si="1"/>
         <v>46196</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>2</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>13</v>
+      </c>
       <c r="H26" s="1">
         <v>20</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
+      </c>
+      <c r="J26" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="3:10" x14ac:dyDescent="0.3">
@@ -8200,21 +8211,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.66666666666666663</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.363636363636363</v>
+        <v>10.478260869565217</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.38</v>
+        <v>0.40166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -8260,7 +8271,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8990,7 +9001,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9696,7 +9707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10423,7 +10434,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11087,7 +11098,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11812,7 +11823,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12539,7 +12550,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -181,7 +181,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>업무 스트레스?</t>
+    <t>업무 스트레스? -&gt; 사람 스트레스겠지…</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1212,7 +1212,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1814,7 +1814,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2547,7 +2547,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3262,7 +3262,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4001,7 +4001,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4752,7 +4752,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5479,7 +5479,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6225,7 +6225,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7584,7 +7584,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8094,16 +8094,20 @@
         <f t="shared" si="1"/>
         <v>46197</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
       <c r="H27" s="1">
         <v>20</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="28" spans="3:10" x14ac:dyDescent="0.3">
@@ -8220,12 +8224,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.478260869565217</v>
+        <v>10.5</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.40166666666666667</v>
+        <v>0.42000000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -8271,7 +8275,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9001,7 +9005,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9707,7 +9711,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10434,7 +10438,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11098,7 +11102,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11823,7 +11827,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12550,7 +12554,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1212,7 +1212,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1814,7 +1814,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2547,7 +2547,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3262,7 +3262,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4001,7 +4001,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4752,7 +4752,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5479,7 +5479,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6225,7 +6225,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7584,7 +7584,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8115,16 +8115,20 @@
         <f t="shared" si="1"/>
         <v>46198</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
       <c r="H28" s="1">
         <v>20</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.3">
@@ -8224,12 +8228,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.5</v>
+        <v>10.48</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.42000000000000004</v>
+        <v>0.4366666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -8275,7 +8279,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9005,7 +9009,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9711,7 +9715,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10438,7 +10442,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11102,7 +11106,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11827,7 +11831,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12554,7 +12558,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1212,7 +1212,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1814,7 +1814,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2547,7 +2547,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3262,7 +3262,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4001,7 +4001,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4752,7 +4752,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5479,7 +5479,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6225,7 +6225,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7584,7 +7584,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8136,16 +8136,20 @@
         <f t="shared" si="1"/>
         <v>46199</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>11</v>
+      </c>
       <c r="H29" s="1">
         <v>20</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="30" spans="3:10" x14ac:dyDescent="0.3">
@@ -8153,16 +8157,20 @@
         <f t="shared" si="1"/>
         <v>46200</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>8</v>
+      </c>
       <c r="H30" s="1">
         <v>20</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.3">
@@ -8170,16 +8178,20 @@
         <f t="shared" si="1"/>
         <v>46201</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
       <c r="H31" s="1">
         <v>20</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.3">
@@ -8219,21 +8231,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.73333333333333328</v>
+        <v>0.8</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.48</v>
+        <v>10.392857142857142</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.4366666666666667</v>
+        <v>0.4850000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8279,7 +8291,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9009,7 +9021,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9715,7 +9727,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10442,7 +10454,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11106,7 +11118,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11831,7 +11843,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12558,7 +12570,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1212,7 +1212,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -1814,7 +1814,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -2547,7 +2547,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -3262,7 +3262,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4001,7 +4001,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -4752,7 +4752,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -5479,7 +5479,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -6225,7 +6225,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -7584,7 +7584,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -8199,16 +8199,20 @@
         <f t="shared" si="1"/>
         <v>46202</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
       <c r="H32" s="1">
         <v>20</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
@@ -8240,12 +8244,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.392857142857142</v>
+        <v>10.379310344827585</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.4850000000000001</v>
+        <v>0.50166666666666671</v>
       </c>
     </row>
   </sheetData>
@@ -8291,7 +8295,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9021,7 +9025,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -9727,7 +9731,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -10454,7 +10458,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11118,7 +11122,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -11843,7 +11847,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">
@@ -12570,7 +12574,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="24" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -13,22 +13,23 @@
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
-    <sheet name="2026-06" sheetId="18" r:id="rId2"/>
-    <sheet name="2026-05" sheetId="17" r:id="rId3"/>
-    <sheet name="2026-04" sheetId="16" r:id="rId4"/>
-    <sheet name="2026-03" sheetId="15" r:id="rId5"/>
-    <sheet name="2026-02" sheetId="14" r:id="rId6"/>
-    <sheet name="2026-01" sheetId="13" r:id="rId7"/>
-    <sheet name="2025-12" sheetId="12" r:id="rId8"/>
-    <sheet name="2025-11" sheetId="11" r:id="rId9"/>
-    <sheet name="2025-10" sheetId="10" r:id="rId10"/>
-    <sheet name="2025-09" sheetId="9" r:id="rId11"/>
-    <sheet name="2025-08" sheetId="8" r:id="rId12"/>
-    <sheet name="2025-07" sheetId="7" r:id="rId13"/>
-    <sheet name="2025-06" sheetId="6" r:id="rId14"/>
-    <sheet name="2025-05" sheetId="5" r:id="rId15"/>
-    <sheet name="2025-04" sheetId="4" r:id="rId16"/>
-    <sheet name="2025-03" sheetId="1" r:id="rId17"/>
+    <sheet name="2026-07" sheetId="19" r:id="rId2"/>
+    <sheet name="2026-06" sheetId="18" r:id="rId3"/>
+    <sheet name="2026-05" sheetId="17" r:id="rId4"/>
+    <sheet name="2026-04" sheetId="16" r:id="rId5"/>
+    <sheet name="2026-03" sheetId="15" r:id="rId6"/>
+    <sheet name="2026-02" sheetId="14" r:id="rId7"/>
+    <sheet name="2026-01" sheetId="13" r:id="rId8"/>
+    <sheet name="2025-12" sheetId="12" r:id="rId9"/>
+    <sheet name="2025-11" sheetId="11" r:id="rId10"/>
+    <sheet name="2025-10" sheetId="10" r:id="rId11"/>
+    <sheet name="2025-09" sheetId="9" r:id="rId12"/>
+    <sheet name="2025-08" sheetId="8" r:id="rId13"/>
+    <sheet name="2025-07" sheetId="7" r:id="rId14"/>
+    <sheet name="2025-06" sheetId="6" r:id="rId15"/>
+    <sheet name="2025-05" sheetId="5" r:id="rId16"/>
+    <sheet name="2025-04" sheetId="4" r:id="rId17"/>
+    <sheet name="2025-03" sheetId="1" r:id="rId18"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="26">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -272,7 +273,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -348,11 +349,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="50">
+  <dxfs count="53">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1212,19 +1246,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -1779,17 +1813,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="47" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1798,6 +1832,712 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46204</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45962</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45963</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I33" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C33" si="1">C5+1</f>
+        <v>45964</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45965</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45966</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45967</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>11</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45968</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45969</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45970</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45971</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45972</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>4</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45973</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>9</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45974</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>9</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45975</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45976</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45977</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45978</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45979</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>8</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45980</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>11</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45981</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>13</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45982</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45983</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>10</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45984</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45985</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45986</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>5</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45987</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45988</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>11</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45989</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45990</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45991</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>10</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D35" s="4">
+        <f>SUM(D4:D33)</f>
+        <v>20</v>
+      </c>
+      <c r="E35" s="5">
+        <f>D35/30</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="1">
+        <f>AVERAGE(G4:G33)</f>
+        <v>9.6333333333333329</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="5">
+        <f>AVERAGE(I4:I33)</f>
+        <v>0.48166666666666674</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C33">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D33">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G33">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1814,19 +2554,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -2511,17 +3251,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2530,7 +3270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2547,19 +3287,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3226,17 +3966,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3245,7 +3985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3262,19 +4002,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3953,6 +4693,760 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.44838709677419353</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46204</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
       </c>
     </row>
   </sheetData>
@@ -3981,761 +5475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46203</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4752,19 +5492,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5443,17 +6183,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5462,7 +6202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5479,19 +6219,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6188,17 +6928,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6208,7 +6948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6225,19 +6965,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6866,17 +7606,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6884,7 +7624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6896,16 +7636,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="24"/>
+      <c r="C2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="25"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="F2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -7554,12 +8294,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7568,6 +8308,608 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46204</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46204</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46205</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>46206</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46207</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46208</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46210</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46211</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46212</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46213</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46214</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46215</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46216</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46217</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46218</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46219</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46220</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46221</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46222</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46223</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46224</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46225</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46226</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46227</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46228</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46229</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46230</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46231</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46232</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46233</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46234</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1" t="e">
+        <f>AVERAGE(G4:G34)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7584,19 +8926,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8220,36 +9562,40 @@
         <f t="shared" si="1"/>
         <v>46203</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="4">
+        <v>2</v>
+      </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1">
+        <v>10</v>
+      </c>
       <c r="H33" s="1">
         <v>20</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0.8</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.379310344827585</v>
+        <v>10.366666666666667</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.50166666666666671</v>
+        <v>0.51833333333333342</v>
       </c>
     </row>
   </sheetData>
@@ -8259,17 +9605,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8278,7 +9624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8295,19 +9641,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8989,17 +10335,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9008,7 +10354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9025,19 +10371,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9695,17 +11041,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9714,7 +11060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9731,19 +11077,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10422,17 +11768,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10441,7 +11787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10458,19 +11804,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11086,17 +12432,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11105,7 +12451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -11122,19 +12468,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11802,6 +13148,733 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46204</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -11828,1437 +13901,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46203</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46203</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45962</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45963</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I33" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C33" si="1">C5+1</f>
-        <v>45964</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>9</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45965</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45966</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45967</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>11</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45968</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45969</v>
-      </c>
-      <c r="D11" s="4">
-        <v>2</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45970</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45971</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>10</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45972</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>4</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45973</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>9</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45974</v>
-      </c>
-      <c r="D16" s="4">
-        <v>2</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>9</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45975</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45976</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45977</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45978</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45979</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>8</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45980</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>11</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45981</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>13</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45982</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>10</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45983</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>10</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45984</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>10</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45985</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>10</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45986</v>
-      </c>
-      <c r="D28" s="4">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>5</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45987</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45988</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>11</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45989</v>
-      </c>
-      <c r="D31" s="4">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45990</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45991</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>10</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D35" s="4">
-        <f>SUM(D4:D33)</f>
-        <v>20</v>
-      </c>
-      <c r="E35" s="5">
-        <f>D35/30</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="1">
-        <f>AVERAGE(G4:G33)</f>
-        <v>9.6333333333333329</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="5">
-        <f>AVERAGE(I4:I33)</f>
-        <v>0.48166666666666674</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -389,21 +389,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2518,17 +2518,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3251,17 +3251,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3966,17 +3966,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4693,760 +4693,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.44838709677419353</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.25" customWidth="1"/>
-    <col min="6" max="6" width="5.25" customWidth="1"/>
-    <col min="7" max="9" width="8.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46204</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45840</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45841</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45842</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45843</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45844</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45845</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>9</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45846</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>45847</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>45848</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>45849</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>45850</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>45851</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>45852</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>45853</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>45854</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>45855</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>45856</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>45857</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>9</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>45858</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>8</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>45859</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>45860</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>45861</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>45862</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>8</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>45863</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>45864</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>45865</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>10</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>45866</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>45867</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>45868</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>45869</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>27</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.87096774193548387</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.096774193548388</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.50483870967741939</v>
-      </c>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="E40" s="8">
-        <f>SUM(D4:D34)/31</f>
-        <v>0.87096774193548387</v>
       </c>
     </row>
   </sheetData>
@@ -5475,6 +4721,760 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="9" width="8.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46204</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45839</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45840</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45841</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45842</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45843</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45844</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45845</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>45847</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>45848</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>45849</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>45851</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>45852</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>45854</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>45855</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>45856</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>45857</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>45858</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>45859</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>45860</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>45861</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>45862</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>45863</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>45864</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>45865</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>45866</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>45867</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>45868</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>45869</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>27</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.096774193548388</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.50483870967741939</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E40" s="8">
+        <f>SUM(D4:D34)/31</f>
+        <v>0.87096774193548387</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
@@ -6183,17 +6183,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6928,17 +6928,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7606,17 +7606,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8294,12 +8294,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C33">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F33">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>14</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8891,21 +8891,22 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9605,17 +9606,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="48" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="47" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10335,17 +10336,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="45" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="44" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11041,17 +11042,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C33">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D33">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G33">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11768,17 +11769,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="38" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12432,17 +12433,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G31">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13148,733 +13149,6 @@
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
         <v>0.54838709677419339</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46204</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
       </c>
     </row>
   </sheetData>
@@ -13901,4 +13175,731 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46204</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="25"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1246,7 +1246,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -1848,7 +1848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -2554,7 +2554,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -3287,7 +3287,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -4002,7 +4002,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -4741,7 +4741,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -5492,7 +5492,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -6219,7 +6219,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -6965,7 +6965,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -8324,7 +8324,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -8342,16 +8342,20 @@
       <c r="C4" s="3">
         <v>46204</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1">
+        <v>8</v>
+      </c>
       <c r="H4" s="1">
         <v>20</v>
       </c>
       <c r="I4" s="5">
         <f>G4/H4</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -8874,14 +8878,14 @@
         <v>0</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="1" t="e">
+      <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>#DIV/0!</v>
+        <v>8</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0</v>
+        <v>1.2903225806451613E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8927,7 +8931,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -9642,7 +9646,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -10372,7 +10376,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -11078,7 +11082,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -11805,7 +11809,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -12469,7 +12473,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -13194,7 +13198,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1246,7 +1246,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -1848,7 +1848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -2554,7 +2554,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -3287,7 +3287,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -4002,7 +4002,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -4741,7 +4741,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -5492,7 +5492,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -6219,7 +6219,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -6965,7 +6965,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -8324,7 +8324,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -8363,16 +8363,20 @@
         <f>C4+1</f>
         <v>46205</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
       <c r="H5" s="1">
         <v>20</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -8871,21 +8875,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>1.2903225806451613E-2</v>
+        <v>2.903225806451613E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8931,7 +8935,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -9646,7 +9650,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -10376,7 +10380,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -11082,7 +11086,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -11809,7 +11813,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -12473,7 +12477,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -13198,7 +13202,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1246,7 +1246,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -1848,7 +1848,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -2554,7 +2554,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -3287,7 +3287,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -4002,7 +4002,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -4741,7 +4741,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -5492,7 +5492,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -6219,7 +6219,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -6965,7 +6965,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -8324,7 +8324,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -8384,16 +8384,20 @@
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46206</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
       <c r="H6" s="1">
         <v>20</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -8401,16 +8405,20 @@
         <f t="shared" si="1"/>
         <v>46207</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
       <c r="H7" s="1">
         <v>20</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -8418,16 +8426,20 @@
         <f t="shared" si="1"/>
         <v>46208</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
       <c r="H8" s="1">
         <v>20</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -8875,21 +8887,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>6.4516129032258063E-2</v>
+        <v>0.12903225806451613</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>2.903225806451613E-2</v>
+        <v>7.7419354838709681E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8935,7 +8947,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -9650,7 +9662,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -10380,7 +10392,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -11086,7 +11098,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -11813,7 +11825,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -12477,7 +12489,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">
@@ -13202,7 +13214,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="25" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="1"/>
+    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885"/>
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="36">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -185,6 +185,46 @@
     <t>업무 스트레스? -&gt; 사람 스트레스겠지…</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>15""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>45""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>55"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -273,7 +313,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -351,6 +391,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1231,19 +1274,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
+  <dimension ref="B2:T36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
         <v>46209</v>
@@ -1259,8 +1307,38 @@
       </c>
       <c r="H3" s="25"/>
       <c r="I3" s="25"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46113</v>
       </c>
@@ -1276,7 +1354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46114</v>
@@ -1293,7 +1371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46115</v>
@@ -1310,7 +1388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46116</v>
@@ -1327,7 +1405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46117</v>
@@ -1344,7 +1422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46118</v>
@@ -1361,7 +1439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46119</v>
@@ -1378,7 +1456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46120</v>
@@ -1395,7 +1473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46121</v>
@@ -1412,7 +1490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46122</v>
@@ -1429,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46123</v>
@@ -1446,7 +1524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46124</v>
@@ -1463,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46125</v>
@@ -8309,19 +8387,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
+  <dimension ref="B2:U36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
         <v>46209</v>
@@ -8337,8 +8419,38 @@
       </c>
       <c r="H3" s="25"/>
       <c r="I3" s="25"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46204</v>
       </c>
@@ -8357,8 +8469,41 @@
         <f>G4/H4</f>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <v>150</v>
+      </c>
+      <c r="L4">
+        <v>162</v>
+      </c>
+      <c r="M4">
+        <v>158</v>
+      </c>
+      <c r="N4">
+        <v>157</v>
+      </c>
+      <c r="O4">
+        <v>159</v>
+      </c>
+      <c r="P4">
+        <v>162</v>
+      </c>
+      <c r="Q4">
+        <v>156</v>
+      </c>
+      <c r="R4">
+        <v>137</v>
+      </c>
+      <c r="S4">
+        <v>128</v>
+      </c>
+      <c r="T4">
+        <v>123</v>
+      </c>
+      <c r="U4" s="26">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46205</v>
@@ -8378,8 +8523,38 @@
         <f t="shared" ref="I5:I34" si="0">G5/H5</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <v>157</v>
+      </c>
+      <c r="L5">
+        <v>159</v>
+      </c>
+      <c r="M5">
+        <v>156</v>
+      </c>
+      <c r="N5">
+        <v>161</v>
+      </c>
+      <c r="O5">
+        <v>158</v>
+      </c>
+      <c r="P5">
+        <v>157</v>
+      </c>
+      <c r="Q5">
+        <v>160</v>
+      </c>
+      <c r="R5">
+        <v>131</v>
+      </c>
+      <c r="S5">
+        <v>124</v>
+      </c>
+      <c r="T5">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46206</v>
@@ -8400,7 +8575,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46207</v>
@@ -8421,7 +8596,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46208</v>
@@ -8441,8 +8616,29 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <v>140</v>
+      </c>
+      <c r="L8">
+        <v>146</v>
+      </c>
+      <c r="M8">
+        <v>140</v>
+      </c>
+      <c r="N8">
+        <v>139</v>
+      </c>
+      <c r="R8">
+        <v>117</v>
+      </c>
+      <c r="S8">
+        <v>104</v>
+      </c>
+      <c r="T8">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46209</v>
@@ -8459,7 +8655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46210</v>
@@ -8476,7 +8672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46211</v>
@@ -8493,7 +8689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46212</v>
@@ -8510,7 +8706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46213</v>
@@ -8527,7 +8723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46214</v>
@@ -8544,7 +8740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46215</v>
@@ -8561,7 +8757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46216</v>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885"/>
+    <workbookView xWindow="33360" yWindow="5715" windowWidth="28800" windowHeight="15885" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
@@ -389,11 +389,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1294,19 +1294,19 @@
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -1926,19 +1926,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -2632,19 +2632,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3365,19 +3365,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4080,19 +4080,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4819,19 +4819,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5570,19 +5570,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6297,19 +6297,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7043,19 +7043,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7714,16 +7714,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="25"/>
+      <c r="C2" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="26"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -8406,19 +8406,19 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -8499,7 +8499,7 @@
       <c r="T4">
         <v>123</v>
       </c>
-      <c r="U4" s="26">
+      <c r="U4" s="25">
         <v>46201</v>
       </c>
     </row>
@@ -8643,16 +8643,50 @@
         <f t="shared" si="1"/>
         <v>46209</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>9</v>
+      </c>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="K9">
+        <v>146</v>
+      </c>
+      <c r="L9">
+        <v>150</v>
+      </c>
+      <c r="M9">
+        <v>154</v>
+      </c>
+      <c r="N9">
+        <v>151</v>
+      </c>
+      <c r="O9">
+        <v>154</v>
+      </c>
+      <c r="P9">
+        <v>152</v>
+      </c>
+      <c r="Q9">
+        <v>156</v>
+      </c>
+      <c r="R9">
+        <v>130</v>
+      </c>
+      <c r="S9">
+        <v>122</v>
+      </c>
+      <c r="T9">
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
@@ -9083,21 +9117,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.12903225806451613</v>
+        <v>0.16129032258064516</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>7.7419354838709681E-2</v>
+        <v>9.1935483870967741E-2</v>
       </c>
     </row>
   </sheetData>
@@ -9143,19 +9177,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9858,19 +9892,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10588,19 +10622,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11294,19 +11328,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -12021,19 +12055,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -12685,19 +12719,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -13410,19 +13444,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="25"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="G3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1294,7 +1294,7 @@
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -1926,7 +1926,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -2632,7 +2632,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -3365,7 +3365,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -4080,7 +4080,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -4819,7 +4819,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -5570,7 +5570,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -6297,7 +6297,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -7043,7 +7043,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8406,7 +8406,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8553,6 +8553,9 @@
       <c r="T5">
         <v>125</v>
       </c>
+      <c r="U5" s="25">
+        <v>46205</v>
+      </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
@@ -8637,6 +8640,9 @@
       <c r="T8">
         <v>103</v>
       </c>
+      <c r="U8" s="25">
+        <v>46208</v>
+      </c>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
@@ -8688,22 +8694,62 @@
       <c r="T9">
         <v>116</v>
       </c>
+      <c r="U9" s="25">
+        <v>46209</v>
+      </c>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46210</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="K10">
+        <v>151</v>
+      </c>
+      <c r="L10">
+        <v>157</v>
+      </c>
+      <c r="M10">
+        <v>155</v>
+      </c>
+      <c r="N10">
+        <v>154</v>
+      </c>
+      <c r="O10">
+        <v>151</v>
+      </c>
+      <c r="P10">
+        <v>154</v>
+      </c>
+      <c r="Q10">
+        <v>160</v>
+      </c>
+      <c r="R10">
+        <v>124</v>
+      </c>
+      <c r="S10">
+        <v>115</v>
+      </c>
+      <c r="T10">
+        <v>111</v>
+      </c>
+      <c r="U10" s="25">
+        <v>46210</v>
       </c>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.3">
@@ -9117,21 +9163,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.16129032258064516</v>
+        <v>0.22580645161290322</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9.5</v>
+        <v>9.5714285714285712</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>9.1935483870967741E-2</v>
+        <v>0.10806451612903226</v>
       </c>
     </row>
   </sheetData>
@@ -9177,7 +9223,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -9892,7 +9938,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -10622,7 +10668,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -11328,7 +11374,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -12055,7 +12101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -12719,7 +12765,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -13444,7 +13490,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1294,7 +1294,7 @@
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -1926,7 +1926,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -2632,7 +2632,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -3365,7 +3365,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -4080,7 +4080,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -4819,7 +4819,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -5570,7 +5570,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -6297,7 +6297,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -7043,7 +7043,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8406,7 +8406,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8757,16 +8757,20 @@
         <f t="shared" si="1"/>
         <v>46211</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.3">
@@ -9172,12 +9176,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9.5714285714285712</v>
+        <v>9.625</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.10806451612903226</v>
+        <v>0.12419354838709677</v>
       </c>
     </row>
   </sheetData>
@@ -9223,7 +9227,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -9938,7 +9942,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -10668,7 +10672,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -11374,7 +11378,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -12101,7 +12105,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -12765,7 +12769,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -13490,7 +13494,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1294,7 +1294,7 @@
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -1926,7 +1926,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -2632,7 +2632,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -3365,7 +3365,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -4080,7 +4080,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -4819,7 +4819,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -5570,7 +5570,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -6297,7 +6297,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -7043,7 +7043,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8406,7 +8406,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8778,16 +8778,53 @@
         <f t="shared" si="1"/>
         <v>46212</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>11</v>
+      </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K12">
+        <v>154</v>
+      </c>
+      <c r="L12">
+        <v>156</v>
+      </c>
+      <c r="M12">
+        <v>152</v>
+      </c>
+      <c r="N12">
+        <v>153</v>
+      </c>
+      <c r="O12">
+        <v>150</v>
+      </c>
+      <c r="P12">
+        <v>151</v>
+      </c>
+      <c r="Q12">
+        <v>155</v>
+      </c>
+      <c r="R12">
+        <v>125</v>
+      </c>
+      <c r="S12">
+        <v>118</v>
+      </c>
+      <c r="T12">
+        <v>114</v>
+      </c>
+      <c r="U12" s="25">
+        <v>46212</v>
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
@@ -9167,21 +9204,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.22580645161290322</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9.625</v>
+        <v>9.7777777777777786</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.12419354838709677</v>
+        <v>0.14193548387096774</v>
       </c>
     </row>
   </sheetData>
@@ -9227,7 +9264,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -9942,7 +9979,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -10672,7 +10709,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -11378,7 +11415,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -12105,7 +12142,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -12769,7 +12806,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -13494,7 +13531,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -52,6 +52,166 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>서진철</author>
+  </authors>
+  <commentList>
+    <comment ref="G15" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이러면</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>안된다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>뭔가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>브레이크가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>필요한</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>듯</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={1FE270D1-E093-46D6-8986-1715CA56D0D3}</author>
@@ -235,7 +395,7 @@
     <numFmt numFmtId="177" formatCode="0.0%"/>
     <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +428,34 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1294,7 +1482,7 @@
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -1926,7 +2114,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -2632,7 +2820,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -3365,7 +3553,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -4080,7 +4268,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -4819,7 +5007,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -5570,7 +5758,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -6297,7 +6485,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -7043,7 +7231,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8386,7 +8574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:U36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8406,7 +8594,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8832,16 +9020,20 @@
         <f t="shared" si="1"/>
         <v>46213</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>9</v>
+      </c>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.3">
@@ -8849,16 +9041,20 @@
         <f t="shared" si="1"/>
         <v>46214</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>9</v>
+      </c>
       <c r="H14" s="1">
         <v>20</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
@@ -8866,16 +9062,20 @@
         <f t="shared" si="1"/>
         <v>46215</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>12</v>
+      </c>
       <c r="H15" s="1">
         <v>20</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
@@ -9204,21 +9404,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.29032258064516131</v>
+        <v>0.32258064516129031</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9.7777777777777786</v>
+        <v>9.8333333333333339</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.14193548387096774</v>
+        <v>0.1903225806451613</v>
       </c>
     </row>
   </sheetData>
@@ -9244,6 +9444,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9264,7 +9465,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -9979,7 +10180,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -10709,7 +10910,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -11415,7 +11616,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -12142,7 +12343,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -12806,7 +13007,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -13531,7 +13732,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -57,6 +57,117 @@
     <author>서진철</author>
   </authors>
   <commentList>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>아침</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>정리</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>끝내고</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>나서</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>...</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G15" authorId="0" shapeId="0">
       <text>
         <r>
@@ -204,6 +315,174 @@
             <family val="2"/>
           </rPr>
           <t>.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G16" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>약간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>멘탈이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>나갔었던</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>날인거</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>같은데</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>잘</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>유지했네</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>..</t>
         </r>
       </text>
     </comment>
@@ -501,7 +780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -582,6 +861,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1482,7 +1764,7 @@
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -2114,7 +2396,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -2820,7 +3102,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -3553,7 +3835,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -4268,7 +4550,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -5007,7 +5289,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -5758,7 +6040,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -6485,7 +6767,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -7231,7 +7513,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8594,7 +8876,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -8650,7 +8932,7 @@
       <c r="G4" s="1">
         <v>8</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="27">
         <v>20</v>
       </c>
       <c r="I4" s="5">
@@ -9083,16 +9365,20 @@
         <f t="shared" si="1"/>
         <v>46216</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
       <c r="H16" s="1">
         <v>20</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
@@ -9413,12 +9699,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9.8333333333333339</v>
+        <v>9.8461538461538467</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.1903225806451613</v>
+        <v>0.20645161290322581</v>
       </c>
     </row>
   </sheetData>
@@ -9465,7 +9751,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -10180,7 +10466,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -10910,7 +11196,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -11616,7 +11902,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -12343,7 +12629,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -13007,7 +13293,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">
@@ -13732,7 +14018,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="26" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -859,11 +859,11 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1744,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:T36"/>
+  <dimension ref="B2:U36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -1753,30 +1753,31 @@
     <col min="12" max="15" width="5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.25" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="0.875" customWidth="1"/>
+    <col min="19" max="21" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,17 +1799,18 @@
       <c r="Q3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="1"/>
+      <c r="S3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46113</v>
       </c>
@@ -1824,7 +1826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46114</v>
@@ -1841,7 +1843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46115</v>
@@ -1858,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46116</v>
@@ -1875,7 +1877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46117</v>
@@ -1892,7 +1894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46118</v>
@@ -1909,7 +1911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46119</v>
@@ -1926,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46120</v>
@@ -1943,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46121</v>
@@ -1960,7 +1962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46122</v>
@@ -1977,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46123</v>
@@ -1994,7 +1996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46124</v>
@@ -2011,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46125</v>
@@ -2396,19 +2398,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3102,19 +3104,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3835,19 +3837,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4550,19 +4552,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5289,19 +5291,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6040,19 +6042,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6767,19 +6769,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7513,19 +7515,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8184,16 +8186,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="26"/>
+      <c r="C2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="27"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="F2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -8857,38 +8859,40 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:U36"/>
+  <dimension ref="B2:V36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
     <col min="11" max="15" width="5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="0.875" customWidth="1"/>
+    <col min="19" max="21" width="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -8910,17 +8914,18 @@
       <c r="Q3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="1"/>
+      <c r="S3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46204</v>
       </c>
@@ -8932,7 +8937,7 @@
       <c r="G4" s="1">
         <v>8</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="26">
         <v>20</v>
       </c>
       <c r="I4" s="5">
@@ -8960,20 +8965,20 @@
       <c r="Q4">
         <v>156</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>137</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>128</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>123</v>
       </c>
-      <c r="U4" s="25">
+      <c r="V4" s="25">
         <v>46201</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46205</v>
@@ -9014,20 +9019,20 @@
       <c r="Q5">
         <v>160</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>131</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>124</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>125</v>
       </c>
-      <c r="U5" s="25">
+      <c r="V5" s="25">
         <v>46205</v>
       </c>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46206</v>
@@ -9048,7 +9053,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46207</v>
@@ -9069,7 +9074,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46208</v>
@@ -9101,20 +9106,20 @@
       <c r="N8">
         <v>139</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>117</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>104</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>103</v>
       </c>
-      <c r="U8" s="25">
+      <c r="V8" s="25">
         <v>46208</v>
       </c>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46209</v>
@@ -9155,20 +9160,20 @@
       <c r="Q9">
         <v>156</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>130</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>122</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>116</v>
       </c>
-      <c r="U9" s="25">
+      <c r="V9" s="25">
         <v>46209</v>
       </c>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46210</v>
@@ -9209,20 +9214,20 @@
       <c r="Q10">
         <v>160</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>124</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>115</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>111</v>
       </c>
-      <c r="U10" s="25">
+      <c r="V10" s="25">
         <v>46210</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46211</v>
@@ -9243,7 +9248,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46212</v>
@@ -9284,20 +9289,20 @@
       <c r="Q12">
         <v>155</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>125</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>118</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>114</v>
       </c>
-      <c r="U12" s="25">
+      <c r="V12" s="25">
         <v>46212</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46213</v>
@@ -9318,7 +9323,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46214</v>
@@ -9339,7 +9344,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46215</v>
@@ -9360,7 +9365,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46216</v>
@@ -9381,24 +9386,61 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <f t="shared" si="1"/>
         <v>46217</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
       <c r="H17" s="1">
         <v>20</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+      <c r="K17">
+        <v>153</v>
+      </c>
+      <c r="L17">
+        <v>160</v>
+      </c>
+      <c r="M17">
+        <v>160</v>
+      </c>
+      <c r="N17">
+        <v>161</v>
+      </c>
+      <c r="O17">
+        <v>158</v>
+      </c>
+      <c r="P17">
+        <v>158</v>
+      </c>
+      <c r="Q17">
+        <v>160</v>
+      </c>
+      <c r="S17">
+        <v>132</v>
+      </c>
+      <c r="T17">
+        <v>122</v>
+      </c>
+      <c r="U17">
+        <v>122</v>
+      </c>
+      <c r="V17" s="25">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <f t="shared" si="1"/>
         <v>46218</v>
@@ -9415,7 +9457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <f t="shared" si="1"/>
         <v>46219</v>
@@ -9432,7 +9474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <f t="shared" si="1"/>
         <v>46220</v>
@@ -9449,7 +9491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <f t="shared" si="1"/>
         <v>46221</v>
@@ -9466,7 +9508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C22" s="3">
         <f t="shared" si="1"/>
         <v>46222</v>
@@ -9483,7 +9525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C23" s="3">
         <f t="shared" si="1"/>
         <v>46223</v>
@@ -9500,7 +9542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <f t="shared" si="1"/>
         <v>46224</v>
@@ -9517,7 +9559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C25" s="3">
         <f t="shared" si="1"/>
         <v>46225</v>
@@ -9534,7 +9576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C26" s="3">
         <f t="shared" si="1"/>
         <v>46226</v>
@@ -9551,7 +9593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C27" s="3">
         <f t="shared" si="1"/>
         <v>46227</v>
@@ -9568,7 +9610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C28" s="3">
         <f t="shared" si="1"/>
         <v>46228</v>
@@ -9585,7 +9627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C29" s="3">
         <f t="shared" si="1"/>
         <v>46229</v>
@@ -9602,7 +9644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C30" s="3">
         <f t="shared" si="1"/>
         <v>46230</v>
@@ -9619,7 +9661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C31" s="3">
         <f t="shared" si="1"/>
         <v>46231</v>
@@ -9636,7 +9678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C32" s="3">
         <f t="shared" si="1"/>
         <v>46232</v>
@@ -9690,21 +9732,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.32258064516129031</v>
+        <v>0.38709677419354838</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9.8461538461538467</v>
+        <v>9.8571428571428577</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.20645161290322581</v>
+        <v>0.22258064516129034</v>
       </c>
     </row>
   </sheetData>
@@ -9751,19 +9793,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -10466,19 +10508,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11196,19 +11238,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11902,19 +11944,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -12629,19 +12671,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -13293,19 +13335,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -14018,19 +14060,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="D3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="27"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="G3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -483,6 +483,194 @@
             <family val="2"/>
           </rPr>
           <t>..</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G18" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>첫번째</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>어김</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이상하게</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>뭔가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>한거</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>같은데</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>아웃풋이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>없었음</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
         </r>
       </text>
     </comment>
@@ -1765,7 +1953,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -2398,7 +2586,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -3104,7 +3292,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -3837,7 +4025,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4552,7 +4740,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -5291,7 +5479,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6042,7 +6230,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6769,7 +6957,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7515,7 +7703,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -8880,7 +9068,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9445,16 +9633,20 @@
         <f t="shared" si="1"/>
         <v>46218</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>12</v>
+      </c>
       <c r="H18" s="1">
         <v>20</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="3:22" x14ac:dyDescent="0.3">
@@ -9741,12 +9933,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>9.8571428571428577</v>
+        <v>10</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.22258064516129034</v>
+        <v>0.24193548387096775</v>
       </c>
     </row>
   </sheetData>
@@ -9793,7 +9985,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -10508,7 +10700,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -11238,7 +11430,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -11944,7 +12136,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -12671,7 +12863,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13335,7 +13527,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -14060,7 +14252,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1953,7 +1953,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -2586,7 +2586,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -3292,7 +3292,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4025,7 +4025,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4740,7 +4740,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -5479,7 +5479,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6230,7 +6230,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6957,7 +6957,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7703,7 +7703,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9068,7 +9068,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9654,16 +9654,20 @@
         <f t="shared" si="1"/>
         <v>46219</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>12</v>
+      </c>
       <c r="H19" s="1">
         <v>20</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="3:22" x14ac:dyDescent="0.3">
@@ -9671,16 +9675,53 @@
         <f t="shared" si="1"/>
         <v>46220</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>8</v>
+      </c>
       <c r="H20" s="1">
         <v>20</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="K20">
+        <v>149</v>
+      </c>
+      <c r="L20">
+        <v>155</v>
+      </c>
+      <c r="M20">
+        <v>159</v>
+      </c>
+      <c r="N20">
+        <v>159</v>
+      </c>
+      <c r="O20">
+        <v>162</v>
+      </c>
+      <c r="P20">
+        <v>168</v>
+      </c>
+      <c r="Q20">
+        <v>167</v>
+      </c>
+      <c r="S20">
+        <v>145</v>
+      </c>
+      <c r="T20">
+        <v>138</v>
+      </c>
+      <c r="U20">
+        <v>131</v>
+      </c>
+      <c r="V20" s="25">
+        <v>46220</v>
       </c>
     </row>
     <row r="21" spans="3:22" x14ac:dyDescent="0.3">
@@ -9688,16 +9729,20 @@
         <f t="shared" si="1"/>
         <v>46221</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>12</v>
+      </c>
       <c r="H21" s="1">
         <v>20</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22" spans="3:22" x14ac:dyDescent="0.3">
@@ -9705,16 +9750,53 @@
         <f t="shared" si="1"/>
         <v>46222</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>12</v>
+      </c>
       <c r="H22" s="1">
         <v>20</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="K22">
+        <v>147</v>
+      </c>
+      <c r="L22">
+        <v>145</v>
+      </c>
+      <c r="M22">
+        <v>144</v>
+      </c>
+      <c r="N22">
+        <v>146</v>
+      </c>
+      <c r="O22">
+        <v>145</v>
+      </c>
+      <c r="P22">
+        <v>148</v>
+      </c>
+      <c r="Q22">
+        <v>150</v>
+      </c>
+      <c r="S22">
+        <v>124</v>
+      </c>
+      <c r="T22">
+        <v>118</v>
+      </c>
+      <c r="U22">
+        <v>114</v>
+      </c>
+      <c r="V22" s="25">
+        <v>46222</v>
       </c>
     </row>
     <row r="23" spans="3:22" x14ac:dyDescent="0.3">
@@ -9924,21 +10006,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.38709677419354838</v>
+        <v>0.54838709677419351</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10</v>
+        <v>10.210526315789474</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.24193548387096775</v>
+        <v>0.31290322580645158</v>
       </c>
     </row>
   </sheetData>
@@ -9985,7 +10067,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -10700,7 +10782,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -11430,7 +11512,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -12136,7 +12218,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -12863,7 +12945,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13527,7 +13609,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -14252,7 +14334,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -662,6 +662,117 @@
             <charset val="129"/>
           </rPr>
           <t>없었음</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G23" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>초심을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>다시</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>찾아야</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>한다</t>
         </r>
         <r>
           <rPr>
@@ -1953,7 +2064,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -2586,7 +2697,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -3292,7 +3403,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4025,7 +4136,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4740,7 +4851,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -5479,7 +5590,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6230,7 +6341,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6957,7 +7068,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7703,7 +7814,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9068,7 +9179,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9804,16 +9915,20 @@
         <f t="shared" si="1"/>
         <v>46223</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>12</v>
+      </c>
       <c r="H23" s="1">
         <v>20</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24" spans="3:22" x14ac:dyDescent="0.3">
@@ -9821,16 +9936,20 @@
         <f t="shared" si="1"/>
         <v>46224</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
       <c r="H24" s="1">
         <v>20</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="3:22" x14ac:dyDescent="0.3">
@@ -10015,12 +10134,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.210526315789474</v>
+        <v>10.285714285714286</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.31290322580645158</v>
+        <v>0.34838709677419349</v>
       </c>
     </row>
   </sheetData>
@@ -10067,7 +10186,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -10782,7 +10901,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -11512,7 +11631,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -12218,7 +12337,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -12945,7 +13064,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13609,7 +13728,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -14334,7 +14453,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -782,6 +782,60 @@
             <family val="2"/>
           </rPr>
           <t>.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G25" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>큰일이네</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>;;;</t>
         </r>
       </text>
     </comment>
@@ -2064,7 +2118,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -2697,7 +2751,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -3403,7 +3457,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4136,7 +4190,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4851,7 +4905,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -5590,7 +5644,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6341,7 +6395,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7068,7 +7122,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7814,7 +7868,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9179,7 +9233,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9957,16 +10011,20 @@
         <f t="shared" si="1"/>
         <v>46225</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
       <c r="H25" s="1">
         <v>20</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26" spans="3:22" x14ac:dyDescent="0.3">
@@ -10125,21 +10183,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.54838709677419351</v>
+        <v>0.58064516129032262</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.285714285714286</v>
+        <v>10.363636363636363</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.34838709677419349</v>
+        <v>0.36774193548387091</v>
       </c>
     </row>
   </sheetData>
@@ -10186,7 +10244,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -10901,7 +10959,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -11631,7 +11689,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -12337,7 +12395,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13064,7 +13122,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13728,7 +13786,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -14453,7 +14511,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2118,7 +2118,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -2751,7 +2751,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -3457,7 +3457,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4190,7 +4190,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4905,7 +4905,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -5644,7 +5644,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6395,7 +6395,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7122,7 +7122,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7868,7 +7868,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9233,7 +9233,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -10032,16 +10032,20 @@
         <f t="shared" si="1"/>
         <v>46226</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>10</v>
+      </c>
       <c r="H26" s="1">
         <v>20</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="3:22" x14ac:dyDescent="0.3">
@@ -10192,12 +10196,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.363636363636363</v>
+        <v>10.347826086956522</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.36774193548387091</v>
+        <v>0.38387096774193546</v>
       </c>
     </row>
   </sheetData>
@@ -10244,7 +10248,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -10959,7 +10963,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -11689,7 +11693,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -12395,7 +12399,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13122,7 +13126,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13786,7 +13790,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -14511,7 +14515,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2118,7 +2118,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -2751,7 +2751,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -3457,7 +3457,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4190,7 +4190,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4905,7 +4905,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -5644,7 +5644,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6395,7 +6395,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7122,7 +7122,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7868,7 +7868,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9233,7 +9233,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -10053,16 +10053,20 @@
         <f t="shared" si="1"/>
         <v>46227</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>9</v>
+      </c>
       <c r="H27" s="1">
         <v>20</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="28" spans="3:22" x14ac:dyDescent="0.3">
@@ -10070,16 +10074,20 @@
         <f t="shared" si="1"/>
         <v>46228</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
       <c r="H28" s="1">
         <v>20</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="3:22" x14ac:dyDescent="0.3">
@@ -10087,16 +10095,20 @@
         <f t="shared" si="1"/>
         <v>46229</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
       <c r="H29" s="1">
         <v>20</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="3:22" x14ac:dyDescent="0.3">
@@ -10104,16 +10116,53 @@
         <f t="shared" si="1"/>
         <v>46230</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>2</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
       <c r="H30" s="1">
         <v>20</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="K30">
+        <v>153</v>
+      </c>
+      <c r="L30">
+        <v>156</v>
+      </c>
+      <c r="M30">
+        <v>164</v>
+      </c>
+      <c r="N30">
+        <v>158</v>
+      </c>
+      <c r="O30">
+        <v>156</v>
+      </c>
+      <c r="P30">
+        <v>160</v>
+      </c>
+      <c r="Q30">
+        <v>160</v>
+      </c>
+      <c r="S30">
+        <v>136</v>
+      </c>
+      <c r="T30">
+        <v>129</v>
+      </c>
+      <c r="U30">
+        <v>127</v>
+      </c>
+      <c r="V30" s="25">
+        <v>46230</v>
       </c>
     </row>
     <row r="31" spans="3:22" x14ac:dyDescent="0.3">
@@ -10121,16 +10170,53 @@
         <f t="shared" si="1"/>
         <v>46231</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>12</v>
+      </c>
       <c r="H31" s="1">
         <v>20</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="K31">
+        <v>157</v>
+      </c>
+      <c r="L31">
+        <v>160</v>
+      </c>
+      <c r="M31">
+        <v>164</v>
+      </c>
+      <c r="N31">
+        <v>163</v>
+      </c>
+      <c r="O31">
+        <v>166</v>
+      </c>
+      <c r="P31">
+        <v>164</v>
+      </c>
+      <c r="Q31">
+        <v>162</v>
+      </c>
+      <c r="S31">
+        <v>138</v>
+      </c>
+      <c r="T31">
+        <v>133</v>
+      </c>
+      <c r="U31">
+        <v>127</v>
+      </c>
+      <c r="V31" s="25">
+        <v>46231</v>
       </c>
     </row>
     <row r="32" spans="3:22" x14ac:dyDescent="0.3">
@@ -10138,16 +10224,20 @@
         <f t="shared" si="1"/>
         <v>46232</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1">
+        <v>13</v>
+      </c>
       <c r="H32" s="1">
         <v>20</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
@@ -10187,21 +10277,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.58064516129032262</v>
+        <v>0.67741935483870963</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.347826086956522</v>
+        <v>10.379310344827585</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.38387096774193546</v>
+        <v>0.48548387096774187</v>
       </c>
     </row>
   </sheetData>
@@ -10248,7 +10338,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -10963,7 +11053,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -11693,7 +11783,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -12399,7 +12489,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13126,7 +13216,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13790,7 +13880,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -14515,7 +14605,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -836,6 +836,79 @@
             <family val="2"/>
           </rPr>
           <t>;;;</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G33" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>휴가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>때문인가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>??</t>
         </r>
       </text>
     </comment>
@@ -2118,7 +2191,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -2751,7 +2824,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -3457,7 +3530,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4190,7 +4263,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -4905,7 +4978,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -5644,7 +5717,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -6395,7 +6468,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7122,7 +7195,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -7868,7 +7941,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -9233,7 +9306,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -10245,16 +10318,20 @@
         <f t="shared" si="1"/>
         <v>46233</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1">
+        <v>14</v>
+      </c>
       <c r="H33" s="1">
         <v>20</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.3">
@@ -10286,12 +10363,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.379310344827585</v>
+        <v>10.5</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.48548387096774187</v>
+        <v>0.50806451612903214</v>
       </c>
     </row>
   </sheetData>
@@ -10338,7 +10415,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -11053,7 +11130,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -11783,7 +11860,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -12489,7 +12566,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13216,7 +13293,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -13880,7 +13957,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">
@@ -14605,7 +14682,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="27" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -13,23 +13,24 @@
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
-    <sheet name="2026-07" sheetId="19" r:id="rId2"/>
-    <sheet name="2026-06" sheetId="18" r:id="rId3"/>
-    <sheet name="2026-05" sheetId="17" r:id="rId4"/>
-    <sheet name="2026-04" sheetId="16" r:id="rId5"/>
-    <sheet name="2026-03" sheetId="15" r:id="rId6"/>
-    <sheet name="2026-02" sheetId="14" r:id="rId7"/>
-    <sheet name="2026-01" sheetId="13" r:id="rId8"/>
-    <sheet name="2025-12" sheetId="12" r:id="rId9"/>
-    <sheet name="2025-11" sheetId="11" r:id="rId10"/>
-    <sheet name="2025-10" sheetId="10" r:id="rId11"/>
-    <sheet name="2025-09" sheetId="9" r:id="rId12"/>
-    <sheet name="2025-08" sheetId="8" r:id="rId13"/>
-    <sheet name="2025-07" sheetId="7" r:id="rId14"/>
-    <sheet name="2025-06" sheetId="6" r:id="rId15"/>
-    <sheet name="2025-05" sheetId="5" r:id="rId16"/>
-    <sheet name="2025-04" sheetId="4" r:id="rId17"/>
-    <sheet name="2025-03" sheetId="1" r:id="rId18"/>
+    <sheet name="2026-08" sheetId="20" r:id="rId2"/>
+    <sheet name="2026-07" sheetId="19" r:id="rId3"/>
+    <sheet name="2026-06" sheetId="18" r:id="rId4"/>
+    <sheet name="2026-05" sheetId="17" r:id="rId5"/>
+    <sheet name="2026-04" sheetId="16" r:id="rId6"/>
+    <sheet name="2026-03" sheetId="15" r:id="rId7"/>
+    <sheet name="2026-02" sheetId="14" r:id="rId8"/>
+    <sheet name="2026-01" sheetId="13" r:id="rId9"/>
+    <sheet name="2025-12" sheetId="12" r:id="rId10"/>
+    <sheet name="2025-11" sheetId="11" r:id="rId11"/>
+    <sheet name="2025-10" sheetId="10" r:id="rId12"/>
+    <sheet name="2025-09" sheetId="9" r:id="rId13"/>
+    <sheet name="2025-08" sheetId="8" r:id="rId14"/>
+    <sheet name="2025-07" sheetId="7" r:id="rId15"/>
+    <sheet name="2025-06" sheetId="6" r:id="rId16"/>
+    <sheet name="2025-05" sheetId="5" r:id="rId17"/>
+    <sheet name="2025-04" sheetId="4" r:id="rId18"/>
+    <sheet name="2025-03" sheetId="1" r:id="rId19"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -945,7 +946,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="36">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1206,7 +1207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1291,11 +1292,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="56">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1313,6 +1317,36 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2191,19 +2225,19 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -2789,17 +2823,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="51" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2808,6 +2842,733 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46238</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>45993</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>45994</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>45995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>45996</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>45997</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>45998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>45999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46000</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46002</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46003</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46004</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46005</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46006</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46007</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46008</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46009</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46010</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46011</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46012</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46013</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46014</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46015</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46017</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46018</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46019</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46020</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>9.935483870967742</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.49677419354838714</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2824,19 +3585,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3513,7 +4274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3530,19 +4291,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4246,7 +5007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4263,19 +5024,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4961,7 +5722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4978,19 +5739,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5697,7 +6458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5717,19 +6478,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6451,7 +7212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6468,19 +7229,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7178,7 +7939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7195,19 +7956,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7924,7 +8685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7941,19 +8702,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8600,7 +9361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8612,16 +9373,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="27"/>
+      <c r="C2" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="28"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="F2" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -9284,6 +10045,658 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:U36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="0.875" customWidth="1"/>
+    <col min="19" max="21" width="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46238</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46235</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46236</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>46237</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46238</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46239</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46240</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46241</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46242</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46243</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46244</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46245</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46246</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46247</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46248</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46249</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46250</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46251</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46252</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46253</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46254</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46255</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46256</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46257</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46258</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46259</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46260</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46261</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46262</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46263</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46264</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46265</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>1</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="51" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9306,19 +10719,19 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -10339,16 +11752,20 @@
         <f t="shared" si="1"/>
         <v>46234</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1">
+        <v>12</v>
+      </c>
       <c r="H34" s="1">
         <v>20</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
@@ -10363,12 +11780,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.5</v>
+        <v>10.548387096774194</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.50806451612903214</v>
+        <v>0.52741935483870961</v>
       </c>
     </row>
   </sheetData>
@@ -10398,7 +11815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10415,19 +11832,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11113,7 +12530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -11130,19 +12547,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -11843,7 +13260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -11860,19 +13277,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -12549,7 +13966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -12566,19 +13983,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -13276,7 +14693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -13293,19 +14710,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -13940,7 +15357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -13957,19 +15374,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
       <c r="F3" s="17"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -14663,731 +16080,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46234</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>45992</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>45993</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>45994</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>45995</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>45996</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>45997</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>45998</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>45999</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>11</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46002</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>12</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46003</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46004</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>8</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46005</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46006</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46007</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46008</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46009</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46010</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46011</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46012</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>8</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46013</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46014</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46015</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46016</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46017</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46018</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46019</v>
-      </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46020</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46022</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.22580645161290322</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>9.935483870967742</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.49677419354838714</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2225,7 +2225,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -2858,7 +2858,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3585,7 +3585,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4291,7 +4291,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5024,7 +5024,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5739,7 +5739,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6478,7 +6478,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7229,7 +7229,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7956,7 +7956,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8702,7 +8702,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10067,7 +10067,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10179,16 +10179,20 @@
         <f t="shared" si="1"/>
         <v>46238</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>12</v>
+      </c>
       <c r="H7" s="1">
         <v>20</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.3">
@@ -10662,12 +10666,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.333333333333334</v>
+        <v>10.75</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.05</v>
+        <v>6.9354838709677416E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10719,7 +10723,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -11832,7 +11836,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12547,7 +12551,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13277,7 +13281,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13983,7 +13987,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14710,7 +14714,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15374,7 +15378,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2225,7 +2225,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -2858,7 +2858,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3585,7 +3585,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4291,7 +4291,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5024,7 +5024,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5739,7 +5739,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6478,7 +6478,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7229,7 +7229,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7956,7 +7956,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8702,7 +8702,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10067,7 +10067,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10200,16 +10200,20 @@
         <f t="shared" si="1"/>
         <v>46239</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
       <c r="H8" s="1">
         <v>20</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.3">
@@ -10657,21 +10661,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>3.2258064516129031E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>6.9354838709677416E-2</v>
+        <v>8.8709677419354843E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10723,7 +10727,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -11836,7 +11840,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12551,7 +12555,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13281,7 +13285,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13987,7 +13991,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14714,7 +14718,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15378,7 +15382,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -946,7 +946,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1089,6 +1089,10 @@
   </si>
   <si>
     <t>03""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>끝나자마자 바로 기록할 필요가 있다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2225,7 +2229,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -2858,7 +2862,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3585,7 +3589,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4291,7 +4295,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5024,7 +5028,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5739,7 +5743,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6478,7 +6482,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7229,7 +7233,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7956,7 +7960,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8702,7 +8706,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10046,28 +10050,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:U36"/>
+  <dimension ref="B2:W36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.5" bestFit="1" customWidth="1"/>
     <col min="12" max="15" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="0.875" customWidth="1"/>
-    <col min="19" max="21" width="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10112,7 +10117,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46235</v>
       </c>
@@ -10132,7 +10137,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46236</v>
@@ -10153,7 +10158,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46237</v>
@@ -10174,7 +10179,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46238</v>
@@ -10195,7 +10200,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46239</v>
@@ -10215,25 +10220,65 @@
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <v>140</v>
+      </c>
+      <c r="L8">
+        <v>150</v>
+      </c>
+      <c r="M8">
+        <v>153</v>
+      </c>
+      <c r="N8">
+        <v>157</v>
+      </c>
+      <c r="O8">
+        <v>154</v>
+      </c>
+      <c r="P8">
+        <v>155</v>
+      </c>
+      <c r="Q8">
+        <v>153</v>
+      </c>
+      <c r="S8">
+        <v>129</v>
+      </c>
+      <c r="T8">
+        <v>121</v>
+      </c>
+      <c r="U8">
+        <v>119</v>
+      </c>
+      <c r="V8" s="25">
+        <v>46239</v>
+      </c>
+      <c r="W8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46240</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>13</v>
+      </c>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46241</v>
@@ -10250,7 +10295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46242</v>
@@ -10267,7 +10312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46243</v>
@@ -10284,7 +10329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46244</v>
@@ -10301,7 +10346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46245</v>
@@ -10318,7 +10363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46246</v>
@@ -10335,7 +10380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46247</v>
@@ -10661,21 +10706,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>6.4516129032258063E-2</v>
+        <v>9.6774193548387094E-2</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11</v>
+        <v>11.333333333333334</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>8.8709677419354843E-2</v>
+        <v>0.10967741935483871</v>
       </c>
     </row>
   </sheetData>
@@ -10727,7 +10772,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -11840,7 +11885,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12555,7 +12600,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13285,7 +13330,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13991,7 +14036,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14718,7 +14763,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15382,7 +15427,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2229,7 +2229,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -2862,7 +2862,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3589,7 +3589,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4295,7 +4295,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5028,7 +5028,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5743,7 +5743,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6482,7 +6482,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7233,7 +7233,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7960,7 +7960,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8706,7 +8706,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10072,7 +10072,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10283,16 +10283,20 @@
         <f t="shared" si="1"/>
         <v>46241</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>12</v>
+      </c>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.3">
@@ -10300,16 +10304,20 @@
         <f t="shared" si="1"/>
         <v>46242</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.3">
@@ -10317,7 +10325,9 @@
         <f t="shared" si="1"/>
         <v>46243</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
@@ -10706,21 +10716,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>9.6774193548387094E-2</v>
+        <v>0.16129032258064516</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.333333333333334</v>
+        <v>11.25</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.10967741935483871</v>
+        <v>0.14516129032258066</v>
       </c>
     </row>
   </sheetData>
@@ -10772,7 +10782,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -11885,7 +11895,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12600,7 +12610,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13330,7 +13340,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14036,7 +14046,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14763,7 +14773,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15427,7 +15437,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2229,7 +2229,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -2862,7 +2862,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3589,7 +3589,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4295,7 +4295,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5028,7 +5028,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5743,7 +5743,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6482,7 +6482,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7233,7 +7233,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7960,7 +7960,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8706,7 +8706,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10072,7 +10072,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10330,13 +10330,15 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>13</v>
+      </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.3">
@@ -10725,12 +10727,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.25</v>
+        <v>11.444444444444445</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.14516129032258066</v>
+        <v>0.16612903225806452</v>
       </c>
     </row>
   </sheetData>
@@ -10782,7 +10784,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -11895,7 +11897,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12610,7 +12612,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13340,7 +13342,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14046,7 +14048,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14773,7 +14775,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15437,7 +15439,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2229,7 +2229,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -2862,7 +2862,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3589,7 +3589,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4295,7 +4295,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5028,7 +5028,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5743,7 +5743,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6482,7 +6482,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7233,7 +7233,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7960,7 +7960,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8706,7 +8706,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10072,7 +10072,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10346,16 +10346,20 @@
         <f t="shared" si="1"/>
         <v>46244</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>13</v>
+      </c>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="14" spans="2:23" x14ac:dyDescent="0.3">
@@ -10727,12 +10731,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.444444444444445</v>
+        <v>11.6</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.16612903225806452</v>
+        <v>0.18709677419354842</v>
       </c>
     </row>
   </sheetData>
@@ -10784,7 +10788,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -11897,7 +11901,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12612,7 +12616,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13342,7 +13346,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14048,7 +14052,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14775,7 +14779,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15439,7 +15443,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2229,7 +2229,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -2862,7 +2862,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3589,7 +3589,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4295,7 +4295,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5028,7 +5028,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5743,7 +5743,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6482,7 +6482,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7233,7 +7233,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7960,7 +7960,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8706,7 +8706,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10072,7 +10072,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10367,16 +10367,20 @@
         <f t="shared" si="1"/>
         <v>46245</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>13</v>
+      </c>
       <c r="H14" s="1">
         <v>20</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="15" spans="2:23" x14ac:dyDescent="0.3">
@@ -10731,12 +10735,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.6</v>
+        <v>11.727272727272727</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.18709677419354842</v>
+        <v>0.20806451612903229</v>
       </c>
     </row>
   </sheetData>
@@ -10788,7 +10792,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -11901,7 +11905,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12616,7 +12620,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13346,7 +13350,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14052,7 +14056,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14779,7 +14783,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15443,7 +15447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -946,7 +946,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="38">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1093,6 +1093,10 @@
   </si>
   <si>
     <t>끝나자마자 바로 기록할 필요가 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEST</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10050,7 +10054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:W36"/>
+  <dimension ref="A2:W36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -10064,12 +10068,12 @@
     <col min="22" max="22" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
         <v>46246</v>
@@ -10117,7 +10121,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46235</v>
       </c>
@@ -10137,7 +10141,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46236</v>
@@ -10158,7 +10162,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46237</v>
@@ -10179,7 +10183,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46238</v>
@@ -10200,7 +10204,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46239</v>
@@ -10257,7 +10261,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46240</v>
@@ -10278,7 +10282,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46241</v>
@@ -10299,7 +10303,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46242</v>
@@ -10320,7 +10324,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46243</v>
@@ -10341,7 +10345,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46244</v>
@@ -10362,7 +10366,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46245</v>
@@ -10383,7 +10387,10 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46246</v>
@@ -10400,7 +10407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46247</v>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -1096,7 +1096,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TEST</t>
+    <t>이게되야 하는데..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -53,6 +53,165 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>서진철</author>
+  </authors>
+  <commentList>
+    <comment ref="G15" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이제</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>좀</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>잡아야</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>할</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>거</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>같은데</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>;;;</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>서진철</author>
@@ -917,7 +1076,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={1FE270D1-E093-46D6-8986-1715CA56D0D3}</author>
@@ -946,7 +1105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1093,10 +1252,6 @@
   </si>
   <si>
     <t>끝나자마자 바로 기록할 필요가 있다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이게되야 하는데..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2233,7 +2388,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -2866,7 +3021,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3593,7 +3748,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4299,7 +4454,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5032,7 +5187,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5747,7 +5902,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6486,7 +6641,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7237,7 +7392,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7964,7 +8119,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8710,7 +8865,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10053,8 +10208,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:W36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:W36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -10068,15 +10223,15 @@
     <col min="22" max="22" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10121,7 +10276,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <v>46235</v>
       </c>
@@ -10141,7 +10296,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C5" s="3">
         <f>C4+1</f>
         <v>46236</v>
@@ -10162,7 +10317,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <f t="shared" ref="C6:C34" si="1">C5+1</f>
         <v>46237</v>
@@ -10183,7 +10338,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>46238</v>
@@ -10204,7 +10359,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>46239</v>
@@ -10261,7 +10416,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>46240</v>
@@ -10282,7 +10437,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>46241</v>
@@ -10303,7 +10458,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>46242</v>
@@ -10324,7 +10479,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>46243</v>
@@ -10345,7 +10500,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>46244</v>
@@ -10366,7 +10521,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>46245</v>
@@ -10387,27 +10542,28 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
+    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>46246</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>14</v>
+      </c>
       <c r="H15" s="1">
         <v>20</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>46247</v>
@@ -10742,12 +10898,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.727272727272727</v>
+        <v>11.916666666666666</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.20806451612903229</v>
+        <v>0.23064516129032261</v>
       </c>
     </row>
   </sheetData>
@@ -10773,6 +10929,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -10799,7 +10956,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -11912,7 +12069,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12627,7 +12784,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13357,7 +13514,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14063,7 +14220,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14790,7 +14947,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15454,7 +15611,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2388,7 +2388,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3021,7 +3021,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3748,7 +3748,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4454,7 +4454,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5187,7 +5187,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5902,7 +5902,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6641,7 +6641,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7392,7 +7392,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8119,7 +8119,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8865,7 +8865,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10231,7 +10231,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10568,16 +10568,20 @@
         <f t="shared" si="1"/>
         <v>46247</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>13</v>
+      </c>
       <c r="H16" s="1">
         <v>20</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
@@ -10889,21 +10893,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.16129032258064516</v>
+        <v>0.19354838709677419</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.916666666666666</v>
+        <v>12</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.23064516129032261</v>
+        <v>0.25161290322580648</v>
       </c>
     </row>
   </sheetData>
@@ -10956,7 +10960,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12069,7 +12073,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12784,7 +12788,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13514,7 +13518,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14220,7 +14224,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14947,7 +14951,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15611,7 +15615,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2388,7 +2388,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3021,7 +3021,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3748,7 +3748,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4454,7 +4454,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5187,7 +5187,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5902,7 +5902,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6641,7 +6641,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7392,7 +7392,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8119,7 +8119,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8865,7 +8865,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10231,7 +10231,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10584,75 +10584,157 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <f t="shared" si="1"/>
         <v>46248</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>13</v>
+      </c>
       <c r="H17" s="1">
         <v>20</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <f t="shared" si="1"/>
         <v>46249</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
       <c r="H18" s="1">
         <v>20</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+      <c r="K18">
+        <v>149</v>
+      </c>
+      <c r="L18">
+        <v>145</v>
+      </c>
+      <c r="M18">
+        <v>149</v>
+      </c>
+      <c r="N18">
+        <v>147</v>
+      </c>
+      <c r="O18">
+        <v>149</v>
+      </c>
+      <c r="P18">
+        <v>153</v>
+      </c>
+      <c r="Q18">
+        <v>155</v>
+      </c>
+      <c r="S18">
+        <v>129</v>
+      </c>
+      <c r="T18">
+        <v>121</v>
+      </c>
+      <c r="U18">
+        <v>117</v>
+      </c>
+      <c r="V18" s="25">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <f t="shared" si="1"/>
         <v>46250</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
       <c r="H19" s="1">
         <v>20</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <f t="shared" si="1"/>
         <v>46251</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
       <c r="H20" s="1">
         <v>20</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+      <c r="K20">
+        <v>158</v>
+      </c>
+      <c r="L20">
+        <v>161</v>
+      </c>
+      <c r="M20">
+        <v>162</v>
+      </c>
+      <c r="N20">
+        <v>161</v>
+      </c>
+      <c r="O20">
+        <v>162</v>
+      </c>
+      <c r="P20">
+        <v>162</v>
+      </c>
+      <c r="Q20">
+        <v>165</v>
+      </c>
+      <c r="S20">
+        <v>135</v>
+      </c>
+      <c r="T20">
+        <v>136</v>
+      </c>
+      <c r="U20">
+        <v>130</v>
+      </c>
+      <c r="V20" s="25">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <f t="shared" si="1"/>
         <v>46252</v>
@@ -10669,7 +10751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C22" s="3">
         <f t="shared" si="1"/>
         <v>46253</v>
@@ -10686,7 +10768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C23" s="3">
         <f t="shared" si="1"/>
         <v>46254</v>
@@ -10703,7 +10785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <f t="shared" si="1"/>
         <v>46255</v>
@@ -10720,7 +10802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C25" s="3">
         <f t="shared" si="1"/>
         <v>46256</v>
@@ -10737,7 +10819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C26" s="3">
         <f t="shared" si="1"/>
         <v>46257</v>
@@ -10754,7 +10836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C27" s="3">
         <f t="shared" si="1"/>
         <v>46258</v>
@@ -10771,7 +10853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C28" s="3">
         <f t="shared" si="1"/>
         <v>46259</v>
@@ -10788,7 +10870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C29" s="3">
         <f t="shared" si="1"/>
         <v>46260</v>
@@ -10805,7 +10887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C30" s="3">
         <f t="shared" si="1"/>
         <v>46261</v>
@@ -10822,7 +10904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C31" s="3">
         <f t="shared" si="1"/>
         <v>46262</v>
@@ -10839,7 +10921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C32" s="3">
         <f t="shared" si="1"/>
         <v>46263</v>
@@ -10893,21 +10975,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.19354838709677419</v>
+        <v>0.25806451612903225</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>12</v>
+        <v>11.705882352941176</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.25161290322580648</v>
+        <v>0.32096774193548389</v>
       </c>
     </row>
   </sheetData>
@@ -10960,7 +11042,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12073,7 +12155,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12788,7 +12870,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13518,7 +13600,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14224,7 +14306,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14951,7 +15033,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15615,7 +15697,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2388,7 +2388,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3021,7 +3021,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3748,7 +3748,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4454,7 +4454,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5187,7 +5187,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5902,7 +5902,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6641,7 +6641,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7392,7 +7392,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8119,7 +8119,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8865,7 +8865,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10231,7 +10231,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10739,16 +10739,20 @@
         <f t="shared" si="1"/>
         <v>46252</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>12</v>
+      </c>
       <c r="H21" s="1">
         <v>20</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22" spans="3:22" x14ac:dyDescent="0.3">
@@ -10984,12 +10988,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.705882352941176</v>
+        <v>11.722222222222221</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.32096774193548389</v>
+        <v>0.3403225806451613</v>
       </c>
     </row>
   </sheetData>
@@ -11042,7 +11046,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12155,7 +12159,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12870,7 +12874,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13600,7 +13604,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14306,7 +14310,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15033,7 +15037,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15697,7 +15701,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -204,6 +204,52 @@
             <family val="2"/>
           </rPr>
           <t>;;;</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G22" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서진철</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>안할거야</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>?</t>
         </r>
       </text>
     </comment>
@@ -2388,7 +2434,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3021,7 +3067,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3748,7 +3794,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4454,7 +4500,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5187,7 +5233,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5902,7 +5948,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6641,7 +6687,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7392,7 +7438,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8119,7 +8165,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8865,7 +8911,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10231,7 +10277,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10760,16 +10806,20 @@
         <f t="shared" si="1"/>
         <v>46253</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>14</v>
+      </c>
       <c r="H22" s="1">
         <v>20</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="23" spans="3:22" x14ac:dyDescent="0.3">
@@ -10988,12 +11038,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.722222222222221</v>
+        <v>11.842105263157896</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.3403225806451613</v>
+        <v>0.36290322580645162</v>
       </c>
     </row>
   </sheetData>
@@ -11046,7 +11096,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12159,7 +12209,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12874,7 +12924,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13604,7 +13654,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14310,7 +14360,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15037,7 +15087,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15701,7 +15751,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2434,7 +2434,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3067,7 +3067,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3794,7 +3794,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4500,7 +4500,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5233,7 +5233,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5948,7 +5948,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6687,7 +6687,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7438,7 +7438,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8165,7 +8165,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8911,7 +8911,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10277,7 +10277,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10827,16 +10827,20 @@
         <f t="shared" si="1"/>
         <v>46254</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>13</v>
+      </c>
       <c r="H23" s="1">
         <v>20</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="24" spans="3:22" x14ac:dyDescent="0.3">
@@ -11029,21 +11033,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.25806451612903225</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.842105263157896</v>
+        <v>11.9</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.36290322580645162</v>
+        <v>0.38387096774193552</v>
       </c>
     </row>
   </sheetData>
@@ -11096,7 +11100,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12209,7 +12213,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12924,7 +12928,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13654,7 +13658,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14360,7 +14364,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15087,7 +15091,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15751,7 +15755,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2434,7 +2434,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3067,7 +3067,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3794,7 +3794,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4500,7 +4500,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5233,7 +5233,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5948,7 +5948,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6687,7 +6687,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7438,7 +7438,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8165,7 +8165,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8911,7 +8911,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10277,7 +10277,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10848,16 +10848,20 @@
         <f t="shared" si="1"/>
         <v>46255</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>14</v>
+      </c>
       <c r="H24" s="1">
         <v>20</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25" spans="3:22" x14ac:dyDescent="0.3">
@@ -10865,16 +10869,20 @@
         <f t="shared" si="1"/>
         <v>46256</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>10</v>
+      </c>
       <c r="H25" s="1">
         <v>20</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="3:22" x14ac:dyDescent="0.3">
@@ -10882,16 +10890,53 @@
         <f t="shared" si="1"/>
         <v>46257</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>10</v>
+      </c>
       <c r="H26" s="1">
         <v>20</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="K26">
+        <v>149</v>
+      </c>
+      <c r="L26">
+        <v>164</v>
+      </c>
+      <c r="M26">
+        <v>165</v>
+      </c>
+      <c r="N26">
+        <v>164</v>
+      </c>
+      <c r="O26">
+        <v>167</v>
+      </c>
+      <c r="P26">
+        <v>166</v>
+      </c>
+      <c r="Q26">
+        <v>163</v>
+      </c>
+      <c r="S26">
+        <v>143</v>
+      </c>
+      <c r="T26">
+        <v>136</v>
+      </c>
+      <c r="U26">
+        <v>134</v>
+      </c>
+      <c r="V26" s="25">
+        <v>46257</v>
       </c>
     </row>
     <row r="27" spans="3:22" x14ac:dyDescent="0.3">
@@ -11033,21 +11078,21 @@
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.29032258064516131</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.9</v>
+        <v>11.826086956521738</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.38387096774193552</v>
+        <v>0.43870967741935485</v>
       </c>
     </row>
   </sheetData>
@@ -11100,7 +11145,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12213,7 +12258,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12928,7 +12973,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13658,7 +13703,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14364,7 +14409,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15091,7 +15136,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15755,7 +15800,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2434,7 +2434,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3067,7 +3067,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3794,7 +3794,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4500,7 +4500,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5233,7 +5233,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5948,7 +5948,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6687,7 +6687,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7438,7 +7438,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8165,7 +8165,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8911,7 +8911,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10277,7 +10277,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10944,16 +10944,20 @@
         <f t="shared" si="1"/>
         <v>46258</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>13</v>
+      </c>
       <c r="H27" s="1">
         <v>20</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="28" spans="3:22" x14ac:dyDescent="0.3">
@@ -11087,12 +11091,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.826086956521738</v>
+        <v>11.875</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.43870967741935485</v>
+        <v>0.45967741935483869</v>
       </c>
     </row>
   </sheetData>
@@ -11145,7 +11149,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12258,7 +12262,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12973,7 +12977,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13703,7 +13707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14409,7 +14413,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15136,7 +15140,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15800,7 +15804,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2434,7 +2434,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3067,7 +3067,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3794,7 +3794,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4500,7 +4500,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5233,7 +5233,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5948,7 +5948,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6687,7 +6687,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7438,7 +7438,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8165,7 +8165,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8911,7 +8911,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10277,7 +10277,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10965,16 +10965,20 @@
         <f t="shared" si="1"/>
         <v>46259</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>13</v>
+      </c>
       <c r="H28" s="1">
         <v>20</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="29" spans="3:22" x14ac:dyDescent="0.3">
@@ -11091,12 +11095,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.875</v>
+        <v>11.92</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.45967741935483869</v>
+        <v>0.48064516129032259</v>
       </c>
     </row>
   </sheetData>
@@ -11149,7 +11153,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12262,7 +12266,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12977,7 +12981,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13707,7 +13711,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14413,7 +14417,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15140,7 +15144,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15804,7 +15808,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2434,7 +2434,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3067,7 +3067,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3794,7 +3794,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4500,7 +4500,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5233,7 +5233,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5948,7 +5948,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6687,7 +6687,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7438,7 +7438,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8165,7 +8165,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8911,7 +8911,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10277,7 +10277,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10986,16 +10986,20 @@
         <f t="shared" si="1"/>
         <v>46260</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>13</v>
+      </c>
       <c r="H29" s="1">
         <v>20</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="30" spans="3:22" x14ac:dyDescent="0.3">
@@ -11095,12 +11099,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.92</v>
+        <v>11.961538461538462</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.48064516129032259</v>
+        <v>0.50161290322580643</v>
       </c>
     </row>
   </sheetData>
@@ -11153,7 +11157,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12266,7 +12270,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12981,7 +12985,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13711,7 +13715,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14417,7 +14421,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15144,7 +15148,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15808,7 +15812,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2434,7 +2434,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3067,7 +3067,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -3794,7 +3794,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -4500,7 +4500,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5233,7 +5233,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -5948,7 +5948,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -6687,7 +6687,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -7438,7 +7438,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8165,7 +8165,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -8911,7 +8911,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -10277,7 +10277,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -11007,16 +11007,20 @@
         <f t="shared" si="1"/>
         <v>46261</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>12</v>
+      </c>
       <c r="H30" s="1">
         <v>20</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31" spans="3:22" x14ac:dyDescent="0.3">
@@ -11099,12 +11103,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.961538461538462</v>
+        <v>11.962962962962964</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.50161290322580643</v>
+        <v>0.5209677419354839</v>
       </c>
     </row>
   </sheetData>
@@ -11157,7 +11161,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12270,7 +12274,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -12985,7 +12989,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -13715,7 +13719,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -14421,7 +14425,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15148,7 +15152,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">
@@ -15812,7 +15816,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="28" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -13,24 +13,25 @@
   </bookViews>
   <sheets>
     <sheet name="_Base" sheetId="2" r:id="rId1"/>
-    <sheet name="2026-08" sheetId="20" r:id="rId2"/>
-    <sheet name="2026-07" sheetId="19" r:id="rId3"/>
-    <sheet name="2026-06" sheetId="18" r:id="rId4"/>
-    <sheet name="2026-05" sheetId="17" r:id="rId5"/>
-    <sheet name="2026-04" sheetId="16" r:id="rId6"/>
-    <sheet name="2026-03" sheetId="15" r:id="rId7"/>
-    <sheet name="2026-02" sheetId="14" r:id="rId8"/>
-    <sheet name="2026-01" sheetId="13" r:id="rId9"/>
-    <sheet name="2025-12" sheetId="12" r:id="rId10"/>
-    <sheet name="2025-11" sheetId="11" r:id="rId11"/>
-    <sheet name="2025-10" sheetId="10" r:id="rId12"/>
-    <sheet name="2025-09" sheetId="9" r:id="rId13"/>
-    <sheet name="2025-08" sheetId="8" r:id="rId14"/>
-    <sheet name="2025-07" sheetId="7" r:id="rId15"/>
-    <sheet name="2025-06" sheetId="6" r:id="rId16"/>
-    <sheet name="2025-05" sheetId="5" r:id="rId17"/>
-    <sheet name="2025-04" sheetId="4" r:id="rId18"/>
-    <sheet name="2025-03" sheetId="1" r:id="rId19"/>
+    <sheet name="2026-09" sheetId="21" r:id="rId2"/>
+    <sheet name="2026-08" sheetId="20" r:id="rId3"/>
+    <sheet name="2026-07" sheetId="19" r:id="rId4"/>
+    <sheet name="2026-06" sheetId="18" r:id="rId5"/>
+    <sheet name="2026-05" sheetId="17" r:id="rId6"/>
+    <sheet name="2026-04" sheetId="16" r:id="rId7"/>
+    <sheet name="2026-03" sheetId="15" r:id="rId8"/>
+    <sheet name="2026-02" sheetId="14" r:id="rId9"/>
+    <sheet name="2026-01" sheetId="13" r:id="rId10"/>
+    <sheet name="2025-12" sheetId="12" r:id="rId11"/>
+    <sheet name="2025-11" sheetId="11" r:id="rId12"/>
+    <sheet name="2025-10" sheetId="10" r:id="rId13"/>
+    <sheet name="2025-09" sheetId="9" r:id="rId14"/>
+    <sheet name="2025-08" sheetId="8" r:id="rId15"/>
+    <sheet name="2025-07" sheetId="7" r:id="rId16"/>
+    <sheet name="2025-06" sheetId="6" r:id="rId17"/>
+    <sheet name="2025-05" sheetId="5" r:id="rId18"/>
+    <sheet name="2025-04" sheetId="4" r:id="rId19"/>
+    <sheet name="2025-03" sheetId="1" r:id="rId20"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -1151,7 +1152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="37">
   <si>
     <t>매일 운동하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1416,7 +1417,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1504,11 +1505,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="59">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1526,6 +1530,36 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2434,19 +2468,19 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -3032,17 +3066,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
       <formula>$B$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="54" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="3" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3067,19 +3101,744 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46023</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1">
+        <v>8</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46024</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C34" si="1">C5+1</f>
+        <v>46025</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46026</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46027</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46028</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46029</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46030</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1">
+        <v>12</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46031</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46032</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1">
+        <v>8</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46033</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1">
+        <v>8</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46034</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1">
+        <v>12</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46035</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1">
+        <v>12</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46036</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46037</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46038</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1">
+        <v>12</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46039</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1">
+        <v>8</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46040</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1">
+        <v>11</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46041</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46042</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1">
+        <v>14</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46043</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1">
+        <v>13</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46044</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1">
+        <v>15</v>
+      </c>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46045</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1">
+        <v>12</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46046</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1">
+        <v>12</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46047</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1">
+        <v>9</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46048</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1">
+        <v>14</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46049</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1">
+        <v>12</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46050</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46051</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46052</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>46053</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1">
+        <v>8</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="4">
+        <f>SUM(D4:D34)</f>
+        <v>17</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/31</f>
+        <v>0.54838709677419351</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1">
+        <f>AVERAGE(G4:G34)</f>
+        <v>10.96774193548387</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="5">
+        <f>AVERAGE(I4:I34)</f>
+        <v>0.54838709677419339</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C34">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D34">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G34">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46265</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -3777,7 +4536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3794,19 +4553,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -4483,7 +5242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4500,19 +5259,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5216,7 +5975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5233,19 +5992,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -5931,7 +6690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5948,19 +6707,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -6667,7 +7426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6687,19 +7446,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -7421,7 +8180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -7438,19 +8197,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8148,7 +8907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8165,19 +8924,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -8894,7 +9653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -8911,19 +9670,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -9570,7 +10329,629 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:U35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="0.875" customWidth="1"/>
+    <col min="19" max="21" width="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B3" s="6">
+        <f ca="1">TODAY()</f>
+        <v>46265</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>46266</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4/H4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <f>C4+1</f>
+        <v>46267</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I33" si="0">G5/H5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <f t="shared" ref="C6:C33" si="1">C5+1</f>
+        <v>46268</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>46269</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>46270</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>46271</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>46272</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>46273</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>46274</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>46275</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>46276</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>46277</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>46278</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>46279</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>46280</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>46281</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>46282</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>46283</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>46284</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>46285</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>46286</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>46287</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>46288</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>46289</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>46290</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>46291</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>46293</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>46294</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>46295</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D35" s="4">
+        <f>SUM(D4:D33)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="5">
+        <f>D35/30</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="1" t="e">
+        <f>AVERAGE(G4:G33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="5">
+        <f>AVERAGE(I4:I33)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:C33">
+    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
+      <formula>$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D33">
+    <cfRule type="cellIs" dxfId="54" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G33">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="greaterThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9582,16 +10963,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="28"/>
+      <c r="C2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="29"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="F2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
@@ -10253,7 +11634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:W36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10277,19 +11658,19 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="27"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -11028,16 +12409,20 @@
         <f t="shared" si="1"/>
         <v>46262</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
       <c r="H31" s="1">
         <v>20</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="3:22" x14ac:dyDescent="0.3">
@@ -11045,36 +12430,77 @@
         <f t="shared" si="1"/>
         <v>46263</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1">
+        <v>12</v>
+      </c>
       <c r="H32" s="1">
         <v>20</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C33" s="3">
         <f t="shared" si="1"/>
         <v>46264</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1">
+        <v>10</v>
+      </c>
       <c r="H33" s="1">
         <v>20</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+      <c r="K33">
+        <v>151</v>
+      </c>
+      <c r="L33">
+        <v>156</v>
+      </c>
+      <c r="M33">
+        <v>157</v>
+      </c>
+      <c r="N33">
+        <v>158</v>
+      </c>
+      <c r="O33">
+        <v>162</v>
+      </c>
+      <c r="P33">
+        <v>158</v>
+      </c>
+      <c r="Q33">
+        <v>163</v>
+      </c>
+      <c r="S33">
+        <v>136</v>
+      </c>
+      <c r="T33">
+        <v>131</v>
+      </c>
+      <c r="U33">
+        <v>120</v>
+      </c>
+      <c r="V33" s="25">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="34" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C34" s="3">
         <f t="shared" si="1"/>
         <v>46265</v>
@@ -11091,24 +12517,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:22" x14ac:dyDescent="0.3">
       <c r="D36" s="4">
         <f>SUM(D4:D34)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E36" s="5">
         <f>D36/31</f>
-        <v>0.35483870967741937</v>
+        <v>0.41935483870967744</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.962962962962964</v>
+        <v>11.833333333333334</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.5209677419354839</v>
+        <v>0.57258064516129048</v>
       </c>
     </row>
   </sheetData>
@@ -11138,7 +12564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -11161,19 +12587,19 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
       <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
@@ -12257,7 +13683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -12274,19 +13700,19 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="22"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -12972,7 +14398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -12989,19 +14415,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -13702,7 +15128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -13719,19 +15145,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -14408,7 +15834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -14425,19 +15851,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -15135,7 +16561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -15152,19 +16578,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
+      <c r="D3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="G3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -15797,729 +17223,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="6">
-        <f ca="1">TODAY()</f>
-        <v>46262</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
-        <v>46023</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1">
-        <v>8</v>
-      </c>
-      <c r="H4" s="1">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <f>G4/H4</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
-        <f>C4+1</f>
-        <v>46024</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I34" si="0">G5/H5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:C34" si="1">C5+1</f>
-        <v>46025</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1">
-        <v>9</v>
-      </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <f t="shared" si="1"/>
-        <v>46026</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <f t="shared" si="1"/>
-        <v>46027</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>46028</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1">
-        <v>9</v>
-      </c>
-      <c r="H9" s="1">
-        <v>20</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <f t="shared" si="1"/>
-        <v>46029</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3">
-        <f t="shared" si="1"/>
-        <v>46030</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1">
-        <v>12</v>
-      </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
-        <f t="shared" si="1"/>
-        <v>46031</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3">
-        <f t="shared" si="1"/>
-        <v>46032</v>
-      </c>
-      <c r="D13" s="4">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1">
-        <v>8</v>
-      </c>
-      <c r="H13" s="1">
-        <v>20</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3">
-        <f t="shared" si="1"/>
-        <v>46033</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
-        <v>8</v>
-      </c>
-      <c r="H14" s="1">
-        <v>20</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3">
-        <f t="shared" si="1"/>
-        <v>46034</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1">
-        <v>12</v>
-      </c>
-      <c r="H15" s="1">
-        <v>20</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3">
-        <f t="shared" si="1"/>
-        <v>46035</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="1">
-        <v>12</v>
-      </c>
-      <c r="H16" s="1">
-        <v>20</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="3">
-        <f t="shared" si="1"/>
-        <v>46036</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="1">
-        <v>11</v>
-      </c>
-      <c r="H17" s="1">
-        <v>20</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="3">
-        <f t="shared" si="1"/>
-        <v>46037</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="1">
-        <v>13</v>
-      </c>
-      <c r="H18" s="1">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="3">
-        <f t="shared" si="1"/>
-        <v>46038</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1">
-        <v>12</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="3">
-        <f t="shared" si="1"/>
-        <v>46039</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1">
-        <v>8</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="3">
-        <f t="shared" si="1"/>
-        <v>46040</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1">
-        <v>11</v>
-      </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="3">
-        <f t="shared" si="1"/>
-        <v>46041</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1">
-        <v>14</v>
-      </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="3">
-        <f t="shared" si="1"/>
-        <v>46042</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1">
-        <v>14</v>
-      </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
-        <f t="shared" si="1"/>
-        <v>46043</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="1">
-        <v>13</v>
-      </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="3">
-        <f t="shared" si="1"/>
-        <v>46044</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1">
-        <v>15</v>
-      </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="3">
-        <f t="shared" si="1"/>
-        <v>46045</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1">
-        <v>12</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="3">
-        <f t="shared" si="1"/>
-        <v>46046</v>
-      </c>
-      <c r="D27" s="4">
-        <v>2</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1">
-        <v>12</v>
-      </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <f t="shared" si="1"/>
-        <v>46047</v>
-      </c>
-      <c r="D28" s="4">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="1">
-        <v>9</v>
-      </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="3">
-        <f t="shared" si="1"/>
-        <v>46048</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="1">
-        <v>14</v>
-      </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="3">
-        <f t="shared" si="1"/>
-        <v>46049</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="1">
-        <v>12</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="3">
-        <f t="shared" si="1"/>
-        <v>46050</v>
-      </c>
-      <c r="D31" s="4">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="1">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="3">
-        <f t="shared" si="1"/>
-        <v>46051</v>
-      </c>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
-        <v>12</v>
-      </c>
-      <c r="H32" s="1">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="3">
-        <f t="shared" si="1"/>
-        <v>46052</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1">
-        <v>12</v>
-      </c>
-      <c r="H33" s="1">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="3">
-        <f t="shared" si="1"/>
-        <v>46053</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D36" s="4">
-        <f>SUM(D4:D34)</f>
-        <v>17</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/31</f>
-        <v>0.54838709677419351</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="1">
-        <f>AVERAGE(G4:G34)</f>
-        <v>10.96774193548387</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="5">
-        <f>AVERAGE(I4:I34)</f>
-        <v>0.54838709677419339</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:C34">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
-      <formula>$B$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D34">
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G34">
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10400,16 +10400,20 @@
       <c r="C4" s="3">
         <v>46266</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
       <c r="H4" s="1">
         <v>20</v>
       </c>
       <c r="I4" s="5">
         <f>G4/H4</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.3">
@@ -10915,14 +10919,14 @@
         <v>0</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="1" t="e">
+      <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>#DIV/0!</v>
+        <v>10</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0</v>
+        <v>1.6666666666666666E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11658,7 +11662,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12505,16 +12509,20 @@
         <f t="shared" si="1"/>
         <v>46265</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="4">
+        <v>0</v>
+      </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1">
+        <v>13</v>
+      </c>
       <c r="H34" s="1">
         <v>20</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="36" spans="3:22" x14ac:dyDescent="0.3">
@@ -12529,12 +12537,12 @@
       <c r="F36" s="5"/>
       <c r="G36" s="1">
         <f>AVERAGE(G4:G34)</f>
-        <v>11.833333333333334</v>
+        <v>11.870967741935484</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="5">
         <f>AVERAGE(I4:I34)</f>
-        <v>0.57258064516129048</v>
+        <v>0.59354838709677427</v>
       </c>
     </row>
   </sheetData>
@@ -12587,7 +12595,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13700,7 +13708,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14415,7 +14423,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15145,7 +15153,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15851,7 +15859,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16578,7 +16586,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10421,16 +10421,20 @@
         <f>C4+1</f>
         <v>46267</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1">
+        <v>11</v>
+      </c>
       <c r="H5" s="1">
         <v>20</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I33" si="0">G5/H5</f>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.3">
@@ -10921,12 +10925,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>1.6666666666666666E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11662,7 +11666,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12595,7 +12599,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13708,7 +13712,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14423,7 +14427,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15153,7 +15157,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15859,7 +15863,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16586,7 +16590,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10442,16 +10442,20 @@
         <f t="shared" ref="C6:C33" si="1">C5+1</f>
         <v>46268</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>13</v>
+      </c>
       <c r="H6" s="1">
         <v>20</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
@@ -10925,12 +10929,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.5</v>
+        <v>11.333333333333334</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>3.5000000000000003E-2</v>
+        <v>5.6666666666666671E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11666,7 +11670,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12599,7 +12603,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13712,7 +13716,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14427,7 +14431,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15157,7 +15161,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15863,7 +15867,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16590,7 +16594,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10463,16 +10463,20 @@
         <f t="shared" si="1"/>
         <v>46269</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
       <c r="H7" s="1">
         <v>20</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.3">
@@ -10480,16 +10484,20 @@
         <f t="shared" si="1"/>
         <v>46270</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
       <c r="H8" s="1">
         <v>20</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.3">
@@ -10497,16 +10505,20 @@
         <f t="shared" si="1"/>
         <v>46271</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>11</v>
+      </c>
       <c r="H9" s="1">
         <v>20</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
@@ -10920,21 +10932,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.333333333333334</v>
+        <v>10.833333333333334</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>5.6666666666666671E-2</v>
+        <v>0.10833333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -11670,7 +11682,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12603,7 +12615,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13716,7 +13728,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14431,7 +14443,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15161,7 +15173,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15867,7 +15879,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16594,7 +16606,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10526,16 +10526,20 @@
         <f t="shared" si="1"/>
         <v>46272</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>14</v>
+      </c>
       <c r="H10" s="1">
         <v>20</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.3">
@@ -10941,12 +10945,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>10.833333333333334</v>
+        <v>11.285714285714286</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.10833333333333334</v>
+        <v>0.13166666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -11682,7 +11686,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12615,7 +12619,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13728,7 +13732,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14443,7 +14447,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15173,7 +15177,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15879,7 +15883,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16606,7 +16610,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10547,16 +10547,20 @@
         <f t="shared" si="1"/>
         <v>46273</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>14</v>
+      </c>
       <c r="H11" s="1">
         <v>20</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.3">
@@ -10945,12 +10949,12 @@
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.285714285714286</v>
+        <v>11.625</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.13166666666666668</v>
+        <v>0.155</v>
       </c>
     </row>
   </sheetData>
@@ -11686,7 +11690,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12619,7 +12623,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13732,7 +13736,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14447,7 +14451,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15177,7 +15181,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15883,7 +15887,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16610,7 +16614,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10568,16 +10568,20 @@
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>13</v>
+      </c>
       <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
@@ -10940,21 +10944,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>3.3333333333333333E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.625</v>
+        <v>11.777777777777779</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.155</v>
+        <v>0.17666666666666669</v>
       </c>
     </row>
   </sheetData>
@@ -11690,7 +11694,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12623,7 +12627,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13736,7 +13740,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14451,7 +14455,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15181,7 +15185,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15887,7 +15891,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16614,7 +16618,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">

--- a/_qDailyReport/_check_System.xlsx
+++ b/_qDailyReport/_check_System.xlsx
@@ -2468,7 +2468,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3101,7 +3101,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -3826,7 +3826,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -4553,7 +4553,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5259,7 +5259,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -5992,7 +5992,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -6707,7 +6707,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -7446,7 +7446,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8197,7 +8197,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -8924,7 +8924,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -9670,7 +9670,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10351,7 +10351,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -10589,16 +10589,20 @@
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>12</v>
+      </c>
       <c r="H13" s="1">
         <v>20</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.3">
@@ -10944,21 +10948,21 @@
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D35" s="4">
         <f>SUM(D4:D33)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="5">
         <f>D35/30</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="1">
         <f>AVERAGE(G4:G33)</f>
-        <v>11.777777777777779</v>
+        <v>11.8</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="5">
         <f>AVERAGE(I4:I33)</f>
-        <v>0.17666666666666669</v>
+        <v>0.19666666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -11694,7 +11698,7 @@
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -12627,7 +12631,7 @@
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -13740,7 +13744,7 @@
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -14455,7 +14459,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15185,7 +15189,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -15891,7 +15895,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
@@ -16618,7 +16622,7 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
